--- a/output/master_jobs.xlsx
+++ b/output/master_jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8080,6 +8080,4055 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Job Search | IBM</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://careers.ibm.com/en_US/careers</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Package Consultant - HRIS/SAP | Apply by 4/20</t>
+        </is>
+      </c>
+      <c r="M94" t="b">
+        <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.ibm.com/en_US/careers', 'strategy': 'INTERACTIVE_DOM', 'parser_used': 'html_basic', 'confidence': 3, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1180, 'output_tokens': 101, 'total_tokens': 1281}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>103326</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Direct Procurement &amp; Research Sourcing - Healthcare &amp; Life Sciences - 103326 - IBM</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://careers.ibm.com/en_US/careers/JobDetail?jobId=103326&amp;amp;source=WEB_Search_INDIA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>['Life Sciences\n                \n\n\n\n\n\n\nBangalore, Karnataka']</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>['Strategic Sourcing', 'Market Analysis', 'Supplier Management', 'Regulatory Compliance', 'Contract Negotiation', 'ERP Systems', 'Data Analysis', 'Risk Management']</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>103326</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="b">
+        <v>1</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.ibm.com/en_US/careers/JobDetail?jobId=103326&amp;amp;source=WEB_Search_INDIA', 'strategy': 'INTERACTIVE_DOM', 'parser_used': 'html_basic', 'confidence': 4, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2426, 'output_tokens': 198, 'total_tokens': 2624}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>41654</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Business-Analyst/41654-en_GB</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>7-8 years</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in engineering, Math, Statistics, Economics, Computer science or related field</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>['SQL', 'Postgres', 'Kafka', 'Agile', 'Python', 'Excel']</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>41654</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M96" t="b">
+        <v>1</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Business-Analyst/41654-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3275, 'output_tokens': 244, 'total_tokens': 3519}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>43704</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Assoc%2C-Technical-Service-Eng%2C-WRB-Tech/43704-en_GB</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in computer science, Information Technology, or related field</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>['AWS', 'Azure', 'GCP', 'Python', 'Bash', 'Ansible', 'Docker', 'Kubernetes', 'Splunk', 'Prometheus', 'Grafana', 'CI/CD', 'Linux', 'Networking fundamentals', 'Security fundamentals']</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>43704</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Pay Charter</t>
+        </is>
+      </c>
+      <c r="M97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Assoc%2C-Technical-Service-Eng%2C-WRB-Tech/43704-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4524, 'output_tokens': 317, 'total_tokens': 4841}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>43705</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Assoc%2C-Technical-Service-Eng%2C-WRB-Tech/43705-en_GB</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in computer science, Information Technology, or related field</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>['AWS', 'Azure', 'GCP', 'Python', 'Bash', 'Ansible', 'Docker', 'Kubernetes', 'Monitoring tools', 'Log analysis', 'CI/CD practices', 'Security and compliance', 'Networking fundamentals', 'Linux/Unix systems']</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>43705</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M98" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Assoc%2C-Technical-Service-Eng%2C-WRB-Tech/43705-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4533, 'output_tokens': 335, 'total_tokens': 4868}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>51912</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Associate-Director-Relationship-Manager-SME-ME/51912-en_GB</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>4-6 years</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>['Substantial experience in banking', 'Experience in SME/Mid Corporate lending']</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>['Relationship Management', 'Financial Analysis', 'Portfolio management']</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>51912</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Associate-Director-Relationship-Manager-SME-ME/51912-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3084, 'output_tokens': 160, 'total_tokens': 3244}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>51913</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>The Engineering Excellence &amp; DevOps team sitting in CCIB organization</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Full-Stack-UI-Developer/51913-en_GB</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>['CI/CD Tools', 'Openshift/EKS', 'Helm Charts', 'Unix Shell Scripts', 'JavaScript', 'Azure', 'AWS', 'SQL']</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>51913</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Full-Stack-UI-Developer/51913-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2822, 'output_tokens': 186, 'total_tokens': 3008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>51917</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/VP-Ops-Excellence/51917-en_GB</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>12-15+ years</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MBA, Master's in Finance, or equivalent</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>['Process mapping', 'Data analysis', 'Automation solutions', 'Regulatory compliance', 'Leadership', 'Change management', 'Stakeholder engagement']</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>51917</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M101" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/VP-Ops-Excellence/51917-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3509, 'output_tokens': 240, 'total_tokens': 3749}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>49875</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Manager-Process-Management-&amp;amp;-Projects/49875-en_GB</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>['Process improvement', 'Complaint management', 'Analytical skills', 'Interpersonal skills', 'Audit handling', 'Cross-geography experience', 'Communication skills', 'Stakeholder management']</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>49875</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M102" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Manager-Process-Management-&amp;amp;-Projects/49875-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2930, 'output_tokens': 174, 'total_tokens': 3104}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>49909</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49909-en_GB</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>['React', 'JavaScript', 'TypeScript', 'CSS', 'Frontend architecture', 'Design patterns', 'Code quality', 'Security tools', 'CI/CD toolchain', 'API integration', 'JSON handling', 'Blockchain frameworks', 'Cryptography', 'DevOps', 'Kubernetes']</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>49909</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49909-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3687, 'output_tokens': 250, 'total_tokens': 3937}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>49910</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49910-en_GB</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>['CI/CD', 'Terraform', 'Git-ops', 'Jenkins', 'Linux', 'Python', 'Kubernetes', 'Docker', 'Hyperledger', 'Corda']</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>49910</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M104" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49910-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2833, 'output_tokens': 195, 'total_tokens': 3028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>49911</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49911-en_GB</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>['Blockchain frameworks', 'Permissioned blockchain', 'DLT applications', 'Backend development', 'Python', 'Golang', 'Solidity', 'RESTful API', 'Microservices', 'Docker', 'Kubernetes', 'Helm', 'AWS', 'Azure', 'Cryptography']</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>49911</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M105" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49911-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3686, 'output_tokens': 336, 'total_tokens': 4022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>49913</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49913-en_GB</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>['Blockchain frameworks', 'Permissioned blockchain', 'DLT applications', 'Backend development', 'Python', 'Golang', 'Solidity', 'RESTful API', 'Microservice architectures', 'Containerization', 'Kubernetes', 'Helm', 'AWS EKS', 'Azure AKS', 'Cryptography']</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>49913</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M106" t="b">
+        <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49913-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3611, 'output_tokens': 253, 'total_tokens': 3864}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>49914</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49914-en_GB</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>['Blockchain frameworks', 'Permissioned blockchain', 'DLT applications', 'Backend development', 'Python', 'Golang', 'Solidity', 'RESTful API', 'Microservice architectures', 'Containerization', 'Kubernetes', 'Helm', 'AWS EKS', 'Azure AKS', 'Cryptography']</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>49914</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M107" t="b">
+        <v>1</v>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49914-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3611, 'output_tokens': 251, 'total_tokens': 3862}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>49923</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49923-en_GB</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>['Project Management', 'Agile experience', 'Planning tools', 'JIRA', 'Confluence', 'Trello', 'MS Office Suite']</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>49923</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M108" t="b">
+        <v>1</v>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49923-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3550, 'output_tokens': 197, 'total_tokens': 3747}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>49928</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49928-en_GB</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>['Blockchain frameworks', 'Permissioned blockchain', 'DLT applications', 'Backend development', 'Python', 'Golang', 'Solidity', 'RESTful API', 'Microservices', 'Docker', 'Kubernetes', 'Helm', 'Cryptography', 'System integration', 'Cloud infrastructure']</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>49928</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M109" t="b">
+        <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49928-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3650, 'output_tokens': 256, 'total_tokens': 3906}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>49929</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49929-en_GB</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>['Blockchain frameworks', 'Permissioned blockchain', 'DLT applications', 'Backend development', 'Python', 'Golang', 'Solidity', 'RESTful API', 'Microservice architectures', 'Containerization', 'Kubernetes', 'Helm', 'AWS EKS', 'Azure AKS', 'Cryptography']</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>49929</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M110" t="b">
+        <v>1</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49929-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3628, 'output_tokens': 243, 'total_tokens': 3871}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>49931</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49931-en_GB</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Relevant degree in Computer Science/Technology</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>['SRE', 'Monitoring Tools', 'Automation Scripts', 'Micro Services', 'Kubernetes', 'AWS']</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>49931</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M111" t="b">
+        <v>1</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49931-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3611, 'output_tokens': 228, 'total_tokens': 3839}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>49933</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49933-en_GB</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>['Project Management', 'Agile experience', 'Clarity PPM', 'JIRA', 'ADO', 'Confluence', 'Trello', 'MS Office Suite']</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>49933</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M112" t="b">
+        <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-App-Development/49933-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3564, 'output_tokens': 233, 'total_tokens': 3797}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>49935</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-Tech-Solutions/49935-en_GB</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>['Agile', 'Scrum', 'Data analysis', 'API design', 'Blockchain', 'Requirement analysis', 'Security best practices']</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>49935</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>payments, account statements, and compliance. Knowledge of API design, implementation, and security bes</t>
+        </is>
+      </c>
+      <c r="M113" t="b">
+        <v>1</v>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-Tech-Solutions/49935-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3792, 'output_tokens': 196, 'total_tokens': 3988}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>49938</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Mgr%2C-Tech-Solutions/49938-en_GB</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>['Project Management', 'Agile', 'DevOps', 'JIRA', 'Confluence', 'PowerPoint', 'MS Office']</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>49938</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M114" t="b">
+        <v>1</v>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Mgr%2C-Tech-Solutions/49938-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3564, 'output_tokens': 200, 'total_tokens': 3764}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>49939</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-App-Development/49939-en_GB</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>['Python', 'Golang', 'Solidity', 'RESTful API', 'Microservice architectures', 'Docker', 'Kubernetes', 'Helm', 'AWS EKS', 'Azure AKS', 'Cryptography', 'Blockchain frameworks']</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>49939</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M115" t="b">
+        <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-App-Development/49939-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3611, 'output_tokens': 222, 'total_tokens': 3833}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>49940</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49940-en_GB</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Computer Science</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>['Test automation tools', 'Selenium', 'Cucumber', 'API testing', 'JIRA', 'SQL', 'Blockchain', 'Smart contracts', 'AI/ML workflows', 'DevOps']</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>49940</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M116" t="b">
+        <v>1</v>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49940-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3992, 'output_tokens': 238, 'total_tokens': 4230}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>45845</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Director-Affluent-Relations/45845-en_GB</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Preferably a Master’s Degree</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>['Retail banking products', 'Customer handling', 'Analytical skills', 'Leadership', 'Communication skills']</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>45845</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M117" t="b">
+        <v>1</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Director-Affluent-Relations/45845-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4043, 'output_tokens': 176, 'total_tokens': 4219}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49941-en_GB</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Computer Science or related</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>['Test automation tools', 'Selenium', 'Cucumber', 'API testing', 'SQL', 'JIRA', 'DevOps', 'Blockchain', 'Smart contracts', 'AI/ML', 'Performance testing', 'Manual testing', 'CI/CD', 'Rest Assured', 'BDD frameworks']</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M118" t="b">
+        <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49941-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3992, 'output_tokens': 235, 'total_tokens': 4227}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>49942</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49942-en_GB</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Computer Science or related</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>['Test automation tools', 'Selenium', 'Cucumber', 'API testing', 'JIRA', 'SQL', 'Blockchain', 'Smart contracts', 'AI/ML workflows', 'DevOps', 'Performance testing', 'Manual testing', 'CI/CD', 'Rest Assured']</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>49942</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M119" t="b">
+        <v>1</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49942-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3992, 'output_tokens': 231, 'total_tokens': 4223}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>49943</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49943-en_GB</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Computer Science</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>['Test automation tools', 'Selenium', 'Cucumber', 'API testing', 'JIRA', 'SQL', 'Blockchain', 'Smart contracts', 'AI/ML workflows', 'DevOps', 'Performance testing', 'Manual testing', 'CI/CD', 'Rest Assured', 'BDD frameworks']</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>49943</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M120" t="b">
+        <v>1</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49943-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3992, 'output_tokens': 282, 'total_tokens': 4274}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>49944</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49944-en_GB</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Computer Science or related</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>['Test automation tools', 'Selenium', 'Cucumber', 'API testing', 'JIRA', 'SQL', 'DevOps', 'Blockchain', 'Smart contracts', 'AI/ML', 'Performance testing', 'Manual testing', 'CI/CD', 'Rest Assured', 'BDD frameworks']</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>49944</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Payments, Decentralized Identity (DID), and smart contract-based financial products.</t>
+        </is>
+      </c>
+      <c r="M121" t="b">
+        <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Automated-Testing/49944-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3990, 'output_tokens': 236, 'total_tokens': 4226}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>49945</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Spl'st, Tech Solutions</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Tech-Solutions/49945-en_GB</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Masters or Engineering background</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>['JSON', 'XML', 'SQL', 'Payments', 'API Design', 'Agile', 'Scrum', 'Blockchain']</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>49945</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>payments, account statements, and compliance. Knowledge of API design, implementation, and security bes</t>
+        </is>
+      </c>
+      <c r="M122" t="b">
+        <v>1</v>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Spl&amp;apos;st%2C-Tech-Solutions/49945-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3803, 'output_tokens': 196, 'total_tokens': 3999}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>51995</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Associate_Manager/51995-en_GB</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>['Gurgaon, IND']</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Graduation/PG</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>['MS Office/Excel', 'Business-Market Knowledge', 'Business – Product and Processes', 'Regulatory Guidelines']</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>51995</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>payments duly met.</t>
+        </is>
+      </c>
+      <c r="M123" t="b">
+        <v>1</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Associate_Manager/51995-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3105, 'output_tokens': 163, 'total_tokens': 3268}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>43806</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Snr-Manager%2C-Data-modelling-Liquidiity/43806-en_GB</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>['SQL', 'Data Solution &amp; Design', 'Analytics and Reporting', 'Technical Business Analyst', 'Application Design']</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>43806</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M124" t="b">
+        <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Snr-Manager%2C-Data-modelling-Liquidiity/43806-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3321, 'output_tokens': 196, 'total_tokens': 3517}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>52008</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Premier-Service-Associate-Manager/52008-en_GB</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Graduate / Postgraduate</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>['Client service', 'Product advice', 'Relationship building', 'Data analysis', 'Communication skills', 'Problem-solving', 'Risk management', 'Stakeholder management']</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>52008</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M125" t="b">
+        <v>1</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Premier-Service-Associate-Manager/52008-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3669, 'output_tokens': 189, 'total_tokens': 3858}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>52009</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Senior-Officer/52009-en_GB</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>University educated</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>['Basic Banking knowledge', 'Communication Skill set']</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>52009</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Payment and Clearing) and Static Data Unit (set up, maintenance, pricing and billing, CoE, LM) in ensur</t>
+        </is>
+      </c>
+      <c r="M126" t="b">
+        <v>1</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Senior-Officer/52009-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2839, 'output_tokens': 134, 'total_tokens': 2973}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>49965</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>We are looking for a highly motivated individual who</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Sr_-Assoc%2C-Prod-Specialist-TAP%2C-WRB-Tech/49965-en_GB</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6 to 12 years</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in computer science or related degree</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>['Triple A Plus', 'Java', 'API', 'WTX', 'Azure DevOps', 'Agile', 'Shell scripting', 'GIT', 'Jenkins', 'Unix commands', 'Problem solving', 'Team spirit']</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>49965</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M127" t="b">
+        <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Sr_-Assoc%2C-Prod-Specialist-TAP%2C-WRB-Tech/49965-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3054, 'output_tokens': 278, 'total_tokens': 3332}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>49988</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Engineering-Lead%2C-Digital-Currencies%2C-Stablecoins/49988-en_GB</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>8+ years</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in computer science, Engineering, Business, or a related field</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>['Agile', 'CI/CD', 'Go', 'Scrum']</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>49988</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>payments systems, stablecoins, and blockchain technologies to effectively coordinate and align teams.</t>
+        </is>
+      </c>
+      <c r="M128" t="b">
+        <v>1</v>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Engineering-Lead%2C-Digital-Currencies%2C-Stablecoins/49988-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3465, 'output_tokens': 278, 'total_tokens': 3743}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>52043</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Manager-Co-creation/52043-en_GB</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>University educated</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>['Go', 'Manage Conduct', 'Manage Risk', 'Manage People', 'Business Facilitation', 'Manage Change', 'Business Governance &amp; Support', 'Management of Frontline Risk', 'Strategy &amp; Business Model', 'Service Delivery &amp; Operations']</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>52043</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Payments as a Service) and VAM (Virtual Account Management) deals, with hands on ownership of lower env</t>
+        </is>
+      </c>
+      <c r="M129" t="b">
+        <v>1</v>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Manager-Co-creation/52043-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4115, 'output_tokens': 222, 'total_tokens': 4337}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Senior-Manager-WRB-Analytics/37709-en_GB</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>5-7+ years</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>['Experience in SQL/HQL', 'Experience in Python', 'Experience in PySpark', 'Knowledge of Dataiku', 'Knowledge of AI tools', 'Banking and financial sector knowledge']</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>['SQL/HQL', 'Python', 'PySpark', 'Dataiku', 'Excel VBA', 'BI tools', 'AI tools']</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Pay Charter</t>
+        </is>
+      </c>
+      <c r="M130" t="b">
+        <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Senior-Manager-WRB-Analytics/37709-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2969, 'output_tokens': 257, 'total_tokens': 3226}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Business-Analyst/43855-en_GB</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>12 years</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Information Technology or Computer Engineering or Similar</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>['Agile', 'Business analysis', 'Stakeholder management', 'Change management', 'Process documentation', 'Risk management', 'SDLC', 'Ado dashboards']</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M131" t="b">
+        <v>1</v>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Business-Analyst/43855-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2940, 'output_tokens': 198, 'total_tokens': 3138}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>52056</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Director%2C-Process-Design/52056-en_GB</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>10+ years</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in business administration, organizational development, or a related field</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>['Process Design', 'Business Architecture', 'Change Management', 'Client Lifecycle Management', 'System Changes', 'Stakeholder Engagement', 'Project Management', 'Lean Six Sigma', 'Data Analysis', 'Workshop Facilitation']</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>52056</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M132" t="b">
+        <v>1</v>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Director%2C-Process-Design/52056-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3477, 'output_tokens': 234, 'total_tokens': 3711}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/VP%2C-Business-Continuity-&amp;amp;-Resilience%2C-TB/50017-en_GB</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>8+ years</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>['8+ years of Transaction Banking experience', 'Hands-on risk management experience', 'Understanding of ERMF', 'Project Management experience']</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>['Risk management frameworks', 'Transaction Banking', 'Resilience, OCIR requirements', 'Communication &amp; Governance skills']</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Pay Charter</t>
+        </is>
+      </c>
+      <c r="M133" t="b">
+        <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/VP%2C-Business-Continuity-&amp;amp;-Resilience%2C-TB/50017-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4245, 'output_tokens': 192, 'total_tokens': 4437}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>52071</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Credit-Analyst-SME-ME/52071-en_GB</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>['Coimbatore, IND']</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Bachelor's or Master's degree in Finance, Accounting, or a related field</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>['Credit Analysis', 'Ratio Analysis', 'Deal Structuring', 'Risk Identification', 'Customer Delight', 'Policy and Compliance']</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>52071</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M134" t="b">
+        <v>1</v>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Credit-Analyst-SME-ME/52071-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2944, 'output_tokens': 238, 'total_tokens': 3182}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>41837</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Senior-Business-Relationship-Manager-Priority-Acquisition/41837-en_GB</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>['Gurgaon, IND']</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>['AMFI certified', 'IRDA certified', 'MS Office']</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>41837</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M135" t="b">
+        <v>1</v>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Senior-Business-Relationship-Manager-Priority-Acquisition/41837-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2428, 'output_tokens': 165, 'total_tokens': 2593}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>52082</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Associate-Director%2C-People-Capability/52082-en_GB</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or higher</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>['Programme or curriculum design', 'Early Careers or Development', 'Digital development tools', 'Content creation', 'English language']</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>52082</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M136" t="b">
+        <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Associate-Director%2C-People-Capability/52082-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3281, 'output_tokens': 217, 'total_tokens': 3498}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>43897</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Intelligence and Analysis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/VP%2C-Technology-&amp;amp;-Cyber-Risk%2C-International-Coverage/43897-en_GB</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Degree in Cyber Security or Technology or equivalent</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>['ICS and Technology Risk Assessment', 'Security frameworks &amp; standards', 'Risk Management Methodologies', 'Threat Intelligence and Analysis', 'Emerging Technologies', 'Communication &amp; Reporting', 'Cyber Security Principles', 'Information Security', 'Stakeholder Management', 'Risk Analysis', 'Regulatory Engagement', 'Risk Frameworks', 'Technical Knowledge', 'Leadership Skills']</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>43897</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M137" t="b">
+        <v>1</v>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/VP%2C-Technology-&amp;amp;-Cyber-Risk%2C-International-Coverage/43897-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3268, 'output_tokens': 309, 'total_tokens': 3577}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>39812</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Manager-Business-Analyst/39812-en_GB</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>8 yrs</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>['Minimum 8 yrs of experience in BA role', 'Experience as BA lead is an advantage', 'Knowledge in SWIFT/ISO 20022', 'Payment background']</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>['Java', 'Spring Boot', 'Kafka Streams', 'REST', 'JSON', 'SWIFT/ISO 20022', 'Stakeholder Management', 'Microservices', 'JIRA', 'Confluence']</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>39812</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>payment and clearing applications.</t>
+        </is>
+      </c>
+      <c r="M138" t="b">
+        <v>1</v>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Manager-Business-Analyst/39812-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3321, 'output_tokens': 251, 'total_tokens': 3572}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>50055</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Assoc%2C-Quality-Eng%2C-WRB-Tech/50055-en_GB</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>7+ years</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Computer Science, Software Engineering, or a related field</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>['Core Java Programming', 'Database Fundamentals', 'Test automation tools', 'Load Runner', 'Unix', 'CI / CD', 'Service virtualization', 'Agile Methodologies', 'Java', 'Python', 'JavaScript', 'Selenium', 'Cucumber', 'Appium', 'JMeter']</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>50055</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M139" t="b">
+        <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Assoc%2C-Quality-Eng%2C-WRB-Tech/50055-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3260, 'output_tokens': 358, 'total_tokens': 3618}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>39816</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Manager-Business-Analyst/39816-en_GB</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>8 yrs</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>['Minimum 8 yrs of experience in BA role', 'Knowledge in SWIFT/ISO 20022', 'Payment background']</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>['Java', 'Spring Boot', 'Kafka Streams', 'REST', 'JSON', 'SWIFT/ISO 20022', 'Stakeholder Management', 'Microservices', 'JIRA', 'Confluence']</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>39816</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>payment and clearing applications.</t>
+        </is>
+      </c>
+      <c r="M140" t="b">
+        <v>1</v>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Manager-Business-Analyst/39816-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3320, 'output_tokens': 243, 'total_tokens': 3563}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>50059</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Portfolio-Manager-Branch/50059-en_GB</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>['Chennai, IND']</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Graduate/ Postgraduate</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>['Banking knowledge', 'Leadership skills', 'Strong Communication Skills', 'Customer Orientation', 'Sales Focus', 'Systems/ Microsoft Office']</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>50059</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M141" t="b">
+        <v>1</v>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Portfolio-Manager-Branch/50059-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3360, 'output_tokens': 168, 'total_tokens': 3528}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>29581</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Job Summary
+This world class leading Bank</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Analyst-Analytics-and-Data-Science%2C-GIAI/29581-en_GB</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>['Bangalore, IND']</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Computer Science, Management Information Systems or Business</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>['Data analysis techniques', 'Programming fundamentals', 'Dashboard Design using Tableau', 'Project management', 'Analytical problem-solving', 'Change management', 'Stakeholder management']</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>29581</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Pay Charter,</t>
+        </is>
+      </c>
+      <c r="M142" t="b">
+        <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Analyst-Analytics-and-Data-Science%2C-GIAI/29581-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 8, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3186, 'output_tokens': 278, 'total_tokens': 3464}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>52137</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Credit-Initiation-Approver/52137-en_GB</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>170 years</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>MBA (Finance) / Chartered Accountant</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>['Underwriting skills', 'PD skills', 'Stakeholder Management', 'Training skills', 'Maintaining TAT', 'Vendor Management']</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>52137</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Pay Charter</t>
+        </is>
+      </c>
+      <c r="M143" t="b">
+        <v>1</v>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Credit-Initiation-Approver/52137-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2822, 'output_tokens': 193, 'total_tokens': 3015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>52138</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Analyst-Manager/52138-en_GB</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>10 years</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>MBA Finance or a CA Qualified</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>['Underwriting Skills', 'Stakeholder Management', 'Vendor Management', 'Negotiation Skills', 'Team Management Skills']</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>52138</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Pay Charter</t>
+        </is>
+      </c>
+      <c r="M144" t="b">
+        <v>1</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Analyst-Manager/52138-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2729, 'output_tokens': 164, 'total_tokens': 2893}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>52140</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Job Details</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://jobs.standardchartered.com/job/Credit-Approver/52140-en_GB</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>10 Years</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>['Mumbai, IND']</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>MBA Finance or CA Qualified</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>['Underwriting Skills', 'Stakeholder Management', 'Vendor Management', 'Negotiation Skills', 'Team Management Skills']</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>52140</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>In line with our Fair Pay Charter</t>
+        </is>
+      </c>
+      <c r="M145" t="b">
+        <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>{'url': 'https://jobs.standardchartered.com/job/Credit-Approver/52140-en_GB', 'strategy': 'dom', 'parser_used': 'html_basic', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2728, 'output_tokens': 252, 'total_tokens': 2980}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/master_jobs.xlsx
+++ b/output/master_jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12070,6 +12070,9934 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>51572617</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RR-0330742</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23196635/rr-0330742-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>7+ years in industry, with a minimum of 3 years in a similar role</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>['Software application development', 'Project coordination', 'Team management', 'Resource allocation', 'Software languages', 'Development methodologies', 'Quality control', 'Leadership skills', 'Communication skills', 'Package applications']</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>51572617</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M145" t="b">
+        <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23196635/rr-0330742-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2386, 'output_tokens': 259, 'total_tokens': 2645}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>51572849</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RR-0329892-Sr Analyst I Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23123606/rr-0329892-sr-analyst-i-infrastructure-services-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>['Active Directory', 'Domain Controllers', 'OU management', 'Group Policy', 'DNS', 'DHCP', 'Kerberos', 'NTLM', 'LDAP', 'SSO', 'ADFS', 'SAML', 'federation', 'Azure AD', 'Entra ID']</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>51572849</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M146" t="b">
+        <v>1</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23123606/rr-0329892-sr-analyst-i-infrastructure-services-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2342, 'output_tokens': 226, 'total_tokens': 2568}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>51559991</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sr Analyst I Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23079040/sr-analyst-i-infrastructure-services-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>5+ years of relevant work experience, minimum 2 years in a similar role</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>['Infrastructure support', 'Technical troubleshooting', 'Infrastructure documentation', 'Data analysis', 'Problem-solving', 'Industry knowledge']</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>51559991</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M147" t="b">
+        <v>1</v>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23079040/sr-analyst-i-infrastructure-services-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2414, 'output_tokens': 207, 'total_tokens': 2621}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>51560535</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Associate Manager Scrum Master</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23071944/associate-manager-scrum-master-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>51560535</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M148" t="b">
+        <v>1</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23071944/associate-manager-scrum-master-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3988, 'output_tokens': 206, 'total_tokens': 4194}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>51573229</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EPS Senior Technical Engineer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23049516/eps-senior-technical-engineer-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>['Base24 eps', 'configuration, scripting, SDK', 'Australian scheme compliance', 'card schemes and formats', 'bank system integration', 'C++, Java', 'Linux, VMware', 'cloud systems (Azure, AWS)', 'ISO 8583, XML', 'VISA, MasterCard, Amex, JCB certifications']</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>51573229</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M149" t="b">
+        <v>1</v>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23049516/eps-senior-technical-engineer-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3085, 'output_tokens': 287, 'total_tokens': 3372}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>51560523</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Senior BASE24 EPS Support</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22666501/senior-base24-eps-support-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>4 to 8 years of hands-on support experience with ACI Base24-eps applications.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>['ISO 8583 messaging systems', 'Base24-eps modules', 'payment networks', 'ATM/POS/Ecom systems', 'support in 24x7 model']</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>51560523</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M150" t="b">
+        <v>1</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22666501/senior-base24-eps-support-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2428, 'output_tokens': 210, 'total_tokens': 2638}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>51564799</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Manager Solution Architecture</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23024388/manager-solution-architecture-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>['Power Apps', 'Power Automate', 'Power BI', 'Google AppSheet', 'ServiceNow', 'AI technologies', 'Project management', 'Communication skills', 'Event hosting', 'Stakeholder engagement', 'Presales experience']</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>51564799</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M151" t="b">
+        <v>1</v>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23024388/manager-solution-architecture-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3040, 'output_tokens': 250, 'total_tokens': 3290}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>51560512</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Base 24 Quality Engineer/Lead</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22666467/base-24-quality-engineer-lead-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>['Gurgaon, Haryana, IN']</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>['Test case development', 'Defect tracking systems', 'Test management tools', 'Quality assurance', 'Switch testing (BASE24, BAE24 EPS, ACI UPF)', 'Payments domain', 'Transaction switch', 'Payment systems', 'E-commerce', 'QA on issuing products', 'Interchange certifications (VISA, MasterCard, Amex, JCB)', 'Testing with simulators and mock environments', 'Automated testing tools', 'JIRA']</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>51560512</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M152" t="b">
+        <v>1</v>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22666467/base-24-quality-engineer-lead-gurgaon-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2496, 'output_tokens': 265, 'total_tokens': 2761}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>51540940</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22665816/project-manager-noida-in/</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 18.0, 'maxValue': 18.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>["Master's degree in related field", 'PMP', 'Scrum Master', 'technical certifications']</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>['Micro Focus tools', 'COBOL', 'JCL', 'CICS', 'DB2 for z/OS', 'Assembler', 'PL/I', 'Rexx', 'GDGs', 'VSAM', 'cloud migration', 'conversion projects']</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>51540940</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M153" t="b">
+        <v>1</v>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22665816/project-manager-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3660, 'output_tokens': 264, 'total_tokens': 3924}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>51560865</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sr Analyst I software Engineering</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23239002/sr-analyst-i-software-engineering-noida-in/</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>51560865</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M154" t="b">
+        <v>1</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23239002/sr-analyst-i-software-engineering-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2193, 'output_tokens': 202, 'total_tokens': 2395}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>51572775</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Analyst I Software Engineering / RR-0346036</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23241916/analyst-i-software-engineering-rr-0346036-indore-in/</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2+ years of relevant software engineering experience</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>['Indore, Madhya Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>['Proficiency in software languages', 'Development methodologies', 'Coding and debugging']</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>51572775</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M155" t="b">
+        <v>1</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23241916/analyst-i-software-engineering-rr-0346036-indore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2396, 'output_tokens': 194, 'total_tokens': 2590}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>51572521</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SAP Senior ABAP Consultant</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23018651/sap-senior-abap-consultant-hyderabad-in/</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>['Hyderabad, Telangana, IN']</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>['8+ years in SAP ABAP development', 'Experience with S/4HANA']</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>['ABAP Objects', 'ALV', 'Enhancements', 'Forms', 'BAPIs', 'BADIs', 'OData', 'SAP Gateway', 'SAP BTP', 'Fiori']</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>51572521</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M156" t="b">
+        <v>1</v>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23018651/sap-senior-abap-consultant-hyderabad-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2675, 'output_tokens': 268, 'total_tokens': 2943}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>51572980</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>RR-0332583 Analyst II Software Engineering</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23242077/rr-0332583-analyst-ii-software-engineering-mumbai-in/</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>['Mumbai, Maharashtra, IN']</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>['Software development', 'Coding', 'Debugging', 'Team collaboration', 'Problem-solving']</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>51572980</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M157" t="b">
+        <v>1</v>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23242077/rr-0332583-analyst-ii-software-engineering-mumbai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2436, 'output_tokens': 186, 'total_tokens': 2622}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>51577007</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sr. Analyst I - Zurich</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23241879/sr-analyst-i-zurich-indore-in/</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>8+ years</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>['Indore, Madhya Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>['Python', 'ML', 'Gen AI', 'NLP', 'GitHub', 'Azure AI Foundry', 'Azure OpenAI GPT', 'Agentic Framework', 'Kubernetes', 'Fine-tuning', 'RAG', 'Prompt engineering', 'Streamlit', 'Flask', 'SQL']</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>51577007</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M158" t="b">
+        <v>1</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23241879/sr-analyst-i-zurich-indore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2096, 'output_tokens': 205, 'total_tokens': 2301}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>51560117</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SAP BASIS HANA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22666510/sap-basis-hana-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>1.0-1000000.0 USD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>['SAP BASIS administration', 'HANA database management', 'SAP S/4HANA', 'Backup and recovery', 'Performance tuning', 'System monitoring', 'Troubleshooting', 'SAP support coordination', 'Security patches', 'Technical documentation']</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>51560117</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M159" t="b">
+        <v>1</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22666510/sap-basis-hana-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2307, 'output_tokens': 228, 'total_tokens': 2535}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>51571763</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Analyst III Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23236731/analyst-iii-infrastructure-services-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>10+2+3 in any stream</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>['Good understanding of computer systems', 'Ability to diagnose technical issues', 'Experience with troubleshooting', 'Interpersonal skills', 'Problem-solving skills', 'Communication skills', 'Organization skills', 'Teamwork ability']</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>51571763</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M160" t="b">
+        <v>1</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23236731/analyst-iii-infrastructure-services-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3942, 'output_tokens': 290, 'total_tokens': 4232}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>51574568</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sr Analyst II Software Engineering</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237106/sr-analyst-ii-software-engineering-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>['NET/.Net Core Framework', 'C#', 'Web API', 'SQL/PostgreSQL', 'JavaScript', 'React', 'Sagas', 'Webpack', 'ES6', 'Jest', 'Enzyme', 'development methodologies', 'software design', 'design patterns', 'GitHub']</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>51574568</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M161" t="b">
+        <v>1</v>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237106/sr-analyst-ii-software-engineering-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2146, 'output_tokens': 261, 'total_tokens': 2407}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>51576160</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sr Analyst II Controllership</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237231/sr-analyst-ii-controllership-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3+ years</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>CA qualified</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>['Financial reporting', 'US GAAP', 'Shared Services', 'Accounting adjustments', 'P&amp;L review', 'Balance sheet analysis', 'SAP knowledge', 'Communication skills']</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>51576160</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M162" t="b">
+        <v>1</v>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237231/sr-analyst-ii-controllership-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2422, 'output_tokens': 201, 'total_tokens': 2623}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>51577521</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Analyst II Finance Operations</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237717/analyst-ii-finance-operations-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>['Payroll processing', 'Statutory compliance', 'Payroll audit', 'Accounting software', 'Employee retirals', 'Internal audit', 'Payroll systems', 'Taxation', 'SAP GHR', 'Workday']</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>51577521</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M163" t="b">
+        <v>1</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237717/analyst-ii-finance-operations-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3086, 'output_tokens': 272, 'total_tokens': 3358}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>51577569</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Service Now Developer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23238971/service-now-developer-noida-in/</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>['ServiceNow CSA (Certified System Administrator)', 'Experience in CSM or FSO']</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>['ServiceNow CSA', 'ServiceNow Development', 'Customer Service Management', 'Financial Services Operations', 'Playbooks', 'Flow Designer', 'Now Assist / AI', 'Platform Analytics', 'Predictive Intelligence', 'Service Portal', 'Catalog Items', 'Automated Test Framework']</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>51577569</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M164" t="b">
+        <v>1</v>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23238971/service-now-developer-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2431, 'output_tokens': 286, 'total_tokens': 2717}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>51540937</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>AMS Project Manager</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22665784/ams-project-manager-noida-in/</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>18+ years in software engineering, 7+ years in managerial roles</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>A master’s degree in a related field is a plus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>['Micro Focus tools', 'COBOL', 'JCL', 'CICS', 'DB2 for z/OS', 'Assembler', 'PL/I', 'Rexx', 'cloud migration', 'conversion projects', 'team leadership', 'project management', 'agile processes', 'software development']</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>51540937</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M165" t="b">
+        <v>1</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22665784/ams-project-manager-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3535, 'output_tokens': 300, 'total_tokens': 3835}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>51569878</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>AWS Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23236820/aws-full-stack-developer-indore-in/</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2+ years of relevant software engineering experience</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>['Indore, Madhya Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>['Software development', 'Coding and debugging', 'Team collaboration', 'Documentation', 'Emerging technologies']</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>51569878</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M166" t="b">
+        <v>1</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23236820/aws-full-stack-developer-indore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2381, 'output_tokens': 192, 'total_tokens': 2573}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>51566944</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Manager Business Process Transactions / RR-0308913</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23236817/manager-business-process-transactions-rr-0308913-noida-in/</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Graduate/Post-Graduate</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>['Transition project leadership', 'Analytical skills', 'Communication skills', 'Transition management tools', 'Business acumen', 'Strategic thinking', 'Teamwork']</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>51566944</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M167" t="b">
+        <v>1</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23236817/manager-business-process-transactions-rr-0308913-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4130, 'output_tokens': 297, 'total_tokens': 4427}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>51564395</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>AWS Devops Terraforms</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22671198/aws-devops-terraforms-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>8+ years in IT, 5+ years as Sr DevOps, 7+ years CI/CD, 1+ years in leadership</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>['AWS provisioning', 'Terraform', 'CloudFormation', 'GitHub', 'GitHub actions', 'Kibana', 'DataDog', 'Dynatrace', 'Akamai', 'Elastic Cache', 'DynamoDB', 'DocumentDB', 'AuroraDB', 'Route 53']</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>51564395</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M168" t="b">
+        <v>1</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22671198/aws-devops-terraforms-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2758, 'output_tokens': 249, 'total_tokens': 3007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>51565665</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Manager Business Process Solutions / RR-0302620</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23236815/manager-business-process-solutions-rr-0302620-noida-in/</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>8–12 years of experience in Quality Management, PMO, or Operations Excellence, with at least 3–5 years in a managerial role.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Graduate/Post-Graduate</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>['ISO 9001, CMMI, Six Sigma', 'Project Management methodologies', 'Risk monitoring and CAPA', 'Error tracking and RCA', 'Stakeholder management', 'Communication skills', 'Analytical and problem-solving', 'Process improvement']</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>51565665</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M169" t="b">
+        <v>1</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23236815/manager-business-process-solutions-rr-0302620-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2945, 'output_tokens': 275, 'total_tokens': 3220}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>51575930</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Workday Integration/Studio Consultant</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237667/workday-integration-studio-consultant-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>['Workday Integration', 'Workday Studio', 'Custom Reports', 'EIBs', 'Connectors', 'XSLT', 'Prototyping', 'Debugging', 'Customer Service', 'Communication Skills']</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>51575930</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M170" t="b">
+        <v>1</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237667/workday-integration-studio-consultant-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2134, 'output_tokens': 240, 'total_tokens': 2374}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>51575874</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Analyst I Software Engineering / RR-0301450</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237112/analyst-i-software-engineering-rr-0301450-noida-in/</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2+ years of relevant software engineering experience</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>['Proficiency in software languages', 'Development methodologies', 'Coding and debugging']</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>51575874</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M171" t="b">
+        <v>1</v>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237112/analyst-i-software-engineering-rr-0301450-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2386, 'output_tokens': 201, 'total_tokens': 2587}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>51565632</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Analyst I Business Process Transactions</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23231613/analyst-i-business-process-transactions-noida-in/</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>['business process transactions', 'process management', 'data analysis', 'quality assurance', 'documentation']</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>51565632</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M172" t="b">
+        <v>1</v>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23231613/analyst-i-business-process-transactions-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2326, 'output_tokens': 185, 'total_tokens': 2511}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>51571149</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Microsoft Dynamics CRM Tech Architect</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22941468/microsoft-dynamics-crm-tech-architect-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Degree in Computer Science or Information Technology-related field</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>['Customization', 'Configuration', 'Plugin', 'Workflow', 'JavaScript', 'C#', 'API integration', 'Power App', 'SSIS', 'Reporting technology', 'Portal management', 'Unit testing', 'DevOps', 'Agile', 'Waterfall']</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>51571149</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M173" t="b">
+        <v>1</v>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22941468/microsoft-dynamics-crm-tech-architect-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2389, 'output_tokens': 270, 'total_tokens': 2659}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>51570209</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator (MySQL, AWS RDS,)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22857716/senior-database-administrator-mysql-aws-rds-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>['MySQL', 'AWS RDS', 'CloudWatch', 'Redshift', 'SQL', 'performance tuning', 'indexing', 'query optimization', 'Amazon Redshift', 'AWS CloudWatch', 'production support', 'backup strategies', 'ETL/ELT', 'infrastructure-as-code', 'CI/CD pipelines']</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>51570209</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M174" t="b">
+        <v>1</v>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22857716/senior-database-administrator-mysql-aws-rds-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2434, 'output_tokens': 272, 'total_tokens': 2706}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>51572278</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Cloud - Intelligent Ops - Automation - 20012026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23221270/cloud-intelligent-ops-automation-20012026-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3+ years in software/cloud engineering (or related)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Bachelors degree or equivalent</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>['Azure Functions', 'Logic Apps', 'Automation Accounts', 'PowerShell', 'Python scripting', 'Azure resource management', 'AI/ML pipelines', 'cloud optimization techniques', 'AI/ML models integration', 'Cognitive Services']</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>51572278</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M175" t="b">
+        <v>1</v>
+      </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23221270/cloud-intelligent-ops-automation-20012026-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2959, 'output_tokens': 250, 'total_tokens': 3209}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>51571043</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SAP Hana FICO Consultant</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22935834/sap-hana-fico-consultant-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>['@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>51571043</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M176" t="b">
+        <v>1</v>
+      </c>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22935834/sap-hana-fico-consultant-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2898, 'output_tokens': 179, 'total_tokens': 3077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>51564507</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SAP ABAP WORKFLOW</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22671214/sap-abap-workflow-hyderabad-in/</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>['Hyderabad, Telangana, IN']</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>['SAP ABAP', 'Workflow', 'S4HANA', 'ABAP Webdynpro', 'ALV reports', 'SAP Fiori', 'SAP ECC', 'SAP S/4HANA', 'EDI standards', 'IDOC data mapping']</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>51564507</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M177" t="b">
+        <v>1</v>
+      </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22671214/sap-abap-workflow-hyderabad-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2629, 'output_tokens': 279, 'total_tokens': 2908}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>51567141</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SAP MM ARIBA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23019014/sap-mm-ariba-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>['SAP MM ARIBA experience', 'SAP S/4HANA', 'Procurement Processes', 'Pricing &amp; Valuation', 'Inventory Functions', 'Integration with SAP modules', 'Supply Chain Collaboration']</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>51567141</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M178" t="b">
+        <v>1</v>
+      </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23019014/sap-mm-ariba-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2246, 'output_tokens': 257, 'total_tokens': 2503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>51572866</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAP Solution Manager and SAP Cloud ALM Expert</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23191435/sap-solution-manager-and-sap-cloud-alm-expert-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3+ years of hands‑on experience in SAP Solution Manager and SAP Cloud ALM.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>['SAP Solution Manager', 'SAP Cloud ALM', 'ChaRM', 'Focused Build', 'SolDoc', 'Project Management', 'Test Management']</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>51572866</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M179" t="b">
+        <v>1</v>
+      </c>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23191435/sap-solution-manager-and-sap-cloud-alm-expert-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2598, 'output_tokens': 195, 'total_tokens': 2793}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>51575977</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>.Net &amp; React.JS Developer</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23216325/-net-react-js-developer-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>['C#', 'ASP.NET', 'React.js', 'JavaScript (ES6+)', 'HTML5', 'CSS3', 'REST APIs', 'JSON', 'Redux', 'SQL Server', 'Git', 'Responsive design']</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>51575977</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M180" t="b">
+        <v>1</v>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23216325/-net-react-js-developer-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2632, 'output_tokens': 333, 'total_tokens': 2965}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>51554359</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>RR-0220901-AssociateManager-Ingenium</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23216312/rr-0220901-associatemanager-ingenium-noida-in/</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>6+ years of relevant work experience, 2+ years in a similar role</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>['Software engineering', 'Leadership', 'Mentoring', 'Project management', 'Software development methodologies', 'Programming skills', 'Debugging skills', 'Communication skills', 'Teamwork']</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>51554359</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M181" t="b">
+        <v>1</v>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23216312/rr-0220901-associatemanager-ingenium-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2854, 'output_tokens': 233, 'total_tokens': 3087}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>51568495</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SAP ABAP &amp; BTP Developer</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22947990/sap-abap-btp-developer-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>['Certification in ABAP for SAP HANA', 'BTP Developer', 'Extensibility']</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>['ABAP, OO-ABAP, CDS, OData, RAP/RESTful ABAP', 'SAP BTP services, CAP/RAP, cloud integration', 'Fiori/UI5 development', 'S/4HANA data models, CDS annotations', 'Security, OAuth, JWT, principal propagation']</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>51568495</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M182" t="b">
+        <v>1</v>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22947990/sap-abap-btp-developer-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3226, 'output_tokens': 304, 'total_tokens': 3530}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>51576447</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Manager Pricing</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23210194/manager-pricing-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 7.0, 'maxValue': 8.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>CA/ CPA/ CMA or MBA in finance</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>51576447</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M183" t="b">
+        <v>1</v>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23210194/manager-pricing-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3486, 'output_tokens': 229, 'total_tokens': 3715}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>51576709</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Senior Snowflake IDMC Developer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23211066/senior-snowflake-idmc-developer-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>6+ Years</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>['Informatica IDMC / IICS', 'Snowflake', 'dbt', 'ETL/ELT workflows', 'Data integration pipelines']</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>51576709</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M184" t="b">
+        <v>1</v>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23211066/senior-snowflake-idmc-developer-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2786, 'output_tokens': 176, 'total_tokens': 2962}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>51576688</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Lead Snowflake IDMC Engineer</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23211038/lead-snowflake-idmc-engineer-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>11+ Years</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>['Snowflake', 'IDMC / IICS', 'dbt', 'ETL/ELT workflows', 'Data integration pipelines']</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>51576688</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M185" t="b">
+        <v>1</v>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23211038/lead-snowflake-idmc-engineer-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2771, 'output_tokens': 171, 'total_tokens': 2942}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>51576711</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Lead Snowflake IDMC Architect</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23211065/lead-snowflake-idmc-architect-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>11+ Years</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>['Snowflake', 'IDMC / IICS', 'Informatica', 'dbt', 'ETL/ELT workflows', 'Data integration', 'Performance optimization', 'Troubleshooting', 'Data governance']</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>51576711</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M186" t="b">
+        <v>1</v>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23211065/lead-snowflake-idmc-architect-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2801, 'output_tokens': 190, 'total_tokens': 2991}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>51568464</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SAP GTS Functional Consultant</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23018990/sap-gts-functional-consultant-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>10+ Years of Relevant experience, Minimum 4 Years in SAP GTS</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>['SAP GTS', 'GTS implementation', 'Compliance management', 'Customs management', 'Risk management', 'SAP GTS E4H', 'SPL Screening', 'Legal regulations', 'SAP-GTS integration', 'ECC', 'S/4HANA', 'OTC SAP-SD', 'Trade reporting']</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>51568464</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M187" t="b">
+        <v>1</v>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23018990/sap-gts-functional-consultant-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2345, 'output_tokens': 221, 'total_tokens': 2566}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>51571710</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>RR-0327794 - Sr Analyst III Software Engineering</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23204310/rr-0327794-sr-analyst-iii-software-engineering-noida-in/</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>3+ years</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>['Software development', 'Testing and debugging', 'Team collaboration', 'Troubleshooting', 'Documentation', 'Emerging technologies', 'Knowledge sharing']</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>51571710</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M188" t="b">
+        <v>1</v>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23204310/rr-0327794-sr-analyst-iii-software-engineering-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2577, 'output_tokens': 188, 'total_tokens': 2765}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>51576009</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Senior Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23204028/senior-azure-data-engineer-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>7+ years</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>['Azure Data Factory', 'Azure Databricks', 'Azure Blob Storage', 'Azure Data Lake', 'Azure Power Apps', 'Azure Functions', 'Azure Data Explorer', 'Python', 'Spark', 'Unix', 'SQL', 'Terraform', 'GitHub', 'MQ']</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>51576009</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M189" t="b">
+        <v>1</v>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23204028/senior-azure-data-engineer-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2488, 'output_tokens': 240, 'total_tokens': 2728}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>51575448</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23204101/devops-engineer-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>6–10+ years in DevOps, SRE, or cloud engineering roles.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>['Azure infrastructure', 'AKS cluster architecture', 'Terraform', 'Ansible', 'Azure DevOps pipelines', 'GitHub Actions', 'PowerShell', 'Bash', 'Python', 'Docker', 'Kubernetes', 'Helm', 'Kustomize', 'AI/automation tools']</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>51575448</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M190" t="b">
+        <v>1</v>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23204101/devops-engineer-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 4170, 'output_tokens': 238, 'total_tokens': 4408}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>51571594</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SAP S4 HANA EWM</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23018959/sap-s4-hana-ewm-pune-in/</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>['Pune, Maharashtra, IN']</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>['SAP EWM configuration', 'Warehouse management', 'SAP modules integration', 'Testing and support', 'Training and documentation', 'Process improvement', 'System analysis', 'Stakeholder collaboration']</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>51571594</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M191" t="b">
+        <v>1</v>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23018959/sap-s4-hana-ewm-pune-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2701, 'output_tokens': 240, 'total_tokens': 2941}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>51571676</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Cloud - FinOps - Global - 16012026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23197112/cloud-finops-global-16012026-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>['FinOps Certified Practitioner', 'Azure or AWS Cloud Certifications', 'multi-cloud cost management platforms']</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>['FinOps principles', 'cloud cost governance', 'AWS, Azure, multi-cloud tools', 'client-facing delivery', 'cloud infrastructure', 'RFPs, solutioning', 'stakeholder management', 'cross-functional collaboration']</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>51571676</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M192" t="b">
+        <v>1</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23197112/cloud-finops-global-16012026-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3268, 'output_tokens': 290, 'total_tokens': 3558}</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>51576701</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23198117/data-engineer-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>5+ years of relevant work experience, minimum 2 years in a similar role</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a relevant field or equivalent</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>['Data processing', 'Data integration', 'Data pipelines', 'Data quality', 'Data standards', 'Data analysis', 'Data engineering tools', 'Data trends', 'Data best practices']</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>51576701</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M193" t="b">
+        <v>1</v>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23198117/data-engineer-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2378, 'output_tokens': 212, 'total_tokens': 2590}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>51564403</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sr Analyst I Software Engineering</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22671200/sr-analyst-i-software-engineering-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>['AWS hands-on experience', 'CI/CD experience', 'Terraform', 'CloudFormation', 'GitHub', 'DataDog', 'Dynatrace', 'ECS Fargate', 'OpenSearch', 'DynamoDB', 'DocumentDB', 'AuroraDB', 'Route 53', 'Elastic Cache Redis']</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>51564403</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M194" t="b">
+        <v>1</v>
+      </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22671200/sr-analyst-i-software-engineering-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2769, 'output_tokens': 315, 'total_tokens': 3084}</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>51576683</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>RR-0342851 - Onsite Manager</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23191432/rr-0342851-onsite-manager-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field or equivalent</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>['IT infrastructure management', 'Team leadership', 'Project management', 'Cybersecurity', 'Vendor management', 'Technical support', 'Training']</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>51576683</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M195" t="b">
+        <v>1</v>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23191432/rr-0342851-onsite-manager-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3746, 'output_tokens': 276, 'total_tokens': 4022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>51575610</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>RR-0352558 - Analyst II Infrastructure Services - LOREAL India</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23186631/rr-0352558-analyst-ii-infrastructure-services-loreal-india-mumbai-in/</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>3 to 5 years of deskside support experience (MNC support experience and VIP support experience preferred)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>['Mumbai, Maharashtra, IN']</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>['Deskside support', 'ServiceNow', 'Infrastructure knowledge', 'Communication skills', 'Coordination skills', 'English fluency', 'Polite and helpful', 'Service mindset', 'Adaptability', 'Overtime willingness']</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>51575610</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M196" t="b">
+        <v>1</v>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23186631/rr-0352558-analyst-ii-infrastructure-services-loreal-india-mumbai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2881, 'output_tokens': 219, 'total_tokens': 3100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>51575986</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Analyst II Finance Operations</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23187090/analyst-ii-finance-operations-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in business administration, finance, accounting or related field preferred</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>['Payroll support', 'Flexi reimbursement policies', 'Income Tax Act', 'SAP', 'Workday', 'Excel', 'Communication skills', 'Interpersonal skills', 'Organizational skills', 'Presentation skills', 'Problem-solving skills', 'Teamwork']</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>51575986</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M197" t="b">
+        <v>1</v>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23187090/analyst-ii-finance-operations-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2680, 'output_tokens': 300, 'total_tokens': 2980}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>51558484</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sr Analyst I Information Security</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22947987/sr-analyst-i-information-security-chennai-in/</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>5+ years of relevant work experience in industry, with a minimum of 2 years in a similar role</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>['Chennai, Tamil Nadu, IN']</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field or equivalent</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>['security assessments', 'audits', 'vulnerability scans', 'security policies', 'security documentation', 'incident response', 'security strategy', 'risk management', 'security trends', 'security awareness', 'security technologies', 'risk assessment', 'industry knowledge', 'technology']</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>51558484</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M198" t="b">
+        <v>1</v>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22947987/sr-analyst-i-information-security-chennai-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2356, 'output_tokens': 261, 'total_tokens': 2617}</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>51557705</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Operations Manager in US Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22935899/operations-manager-in-us-life-annuities-noida-in/</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>{'@type': 'MonetaryAmount', 'currency': 'USD', 'value': {'@type': 'QuantitativeValue', 'minValue': 1.0, 'maxValue': 1000000.0, 'unitText': 'YEAR'}}</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>['Noida, Uttar Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Graduate in any stream</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>['Leadership in US Insurance', 'People management', 'Communication skills', 'Data-driven decision making', 'Client relationship management', 'Operational metrics understanding', 'Proficiency in Excel, Power BI, PowerPoint']</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>51557705</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M199" t="b">
+        <v>1</v>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22935899/operations-manager-in-us-life-annuities-noida-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 3183, 'output_tokens': 279, 'total_tokens': 3462}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>51576216</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Associate Manager Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23188100/associate-manager-infrastructure-services-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>6+ years of relevant work experience, 2+ years in a similar role</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>['Infrastructure management', 'Teamwork', 'Troubleshooting', 'Documentation', 'Resource optimization']</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>51576216</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M200" t="b">
+        <v>1</v>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23188100/associate-manager-infrastructure-services-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2418, 'output_tokens': 180, 'total_tokens': 2598}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>51576215</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Analyst I Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23187071/analyst-i-infrastructure-services-bangalore-in/</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>['Bangalore, Karnataka, IN']</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>['Data analysis', 'Problem-solving', 'Infrastructure support']</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>51576215</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M201" t="b">
+        <v>1</v>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23187071/analyst-i-infrastructure-services-bangalore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2357, 'output_tokens': 172, 'total_tokens': 2529}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>51543115</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TransAmerica Associate Manager - RR-0150088</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23237305/transamerica-associate-manager-rr-0150088-indore-in/</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>6+ years in industry, with a minimum of 2+ years in a similar role</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>['Indore, Madhya Pradesh, IN']</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>['Software development', 'Team leadership', 'Code reviews', 'Project management', 'Mentorship', 'Programming languages', 'Development methodologies', 'Communication skills', 'Time management']</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>51543115</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD 1.0-1000000.0</t>
+        </is>
+      </c>
+      <c r="M202" t="b">
+        <v>1</v>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23237305/transamerica-associate-manager-rr-0150088-indore-in/', 'strategy': 'dom', 'parser_used': 'json_ld', 'confidence': 7, 'ai_forced': True, 'preferred_skills': [], 'tools_and_technologies': [], 'certifications': [], 'soft_skills': [], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2598, 'output_tokens': 225, 'total_tokens': 2823}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="b">
+        <v>1</v>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>{'url': '', 'strategy': 'api', 'site_type': 'DYNAMIC_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>453325-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Associate AP Invoice Processing Process Expert</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Kolkata-%28ex-Calcutta%29-Associate-AP-Invoice-Processing-Process-Expert/1382142133/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Executives</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>['IN, Kolkata']</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>['Process Invoicing', 'Finance', 'Operations Management', 'Customer Service', 'Team Building', 'Stakeholder Management']</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Posted 4 Days Ago</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>453325-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="b">
+        <v>1</v>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'Role based in BSv organisation. Leveraging expert knowledge of Process Invoiceing, The Process Invoicing Process Experts participate of in or lead the achievement of service levels, key measurement targets of the team and delivers a high quality and cost-effective service that drive compelling business outcomes. They ensure the delivery of a customer focused and compliant services through the adoption of frictionless finance, practice processes, technologies, methodologies which drive innovation and process improvements. They will manage the contract on a daily basis including operations and finance and complex operational issues and ensure that operations are run according to budget. They will build and develop the team. Their expert domain expertise means they process more complex transactions and producing outputs across Invoice processing activities and manage effective usage of resources in the service delivery.'}, {'section_title': 'Key Responsibilities', 'content': 'Supports experienced Finance specialists delivering progress reporting, task management and documentation for Finance activity.'}]</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Kolkata-%28ex-Calcutta%29-Associate-AP-Invoice-Processing-Process-Expert/1382142133/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Finance', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1145, 'output_tokens': 557, 'total_tokens': 1702}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>453321-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AP Invoice Processing Process Expert</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Kolkata-%28ex-Calcutta%29-AP-Invoice-Processing-Process-Expert/1382149433/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Executives</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>['IN, Kolkata']</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>['Process Invoicing', 'Finance support', 'Stakeholder management', 'Operational management', 'Team development']</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Posted 6 Days Ago</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>453321-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="b">
+        <v>1</v>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'Role based in BSv organisation. Leveraging expert knowledge of Process Invoiceing, The Process Invoicing Process Experts participate of in or lead the achievement of service levels, key measurement targets of the team and delivers a high quality and cost-effective service that drive compelling business outcomes. They ensure the delivery of a customer focused and compliant services through the adoption of frictionless finance, practice processes, technologies, methodologies which drive innovation and process improvements. They will manage the contract on a daily basis including operations and finance and complex operational issues and ensure that operations are run according to budget. They will build and develop the team. Their expert domain expertise means they process more complex transactions and producing outputs across Invoice processing activities and manage effective usage of resources in the service delivery.'}, {'section_title': 'Key Responsibilities', 'content': 'Operating as a Finance specialist supporting small and medium sized finance exercises. Building skills for a more specialized Finance service. May start to manage others. Manage working relationships with stakeholders for the supported business areas. Able to act on own initiative but will require supervision.'}]</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Kolkata-%28ex-Calcutta%29-AP-Invoice-Processing-Process-Expert/1382149433/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Finance', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1148, 'output_tokens': 588, 'total_tokens': 1736}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>396843-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ServiceNow Solutioner Leader</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Gurgaon-ServiceNow-Solutioner-Leader/1292679801/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Experienced Professionals</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>['ServiceNow platform', 'Solution design', 'Pre-sales consulting', 'Customer engagement', 'Solution demonstrations', 'Technical presentation', 'Cloud platforms', 'Scripting languages (JavaScript)', 'Web technologies (REST, SOAP, HTML)']</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-02-11T12:58:47.000Z</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>396843-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="b">
+        <v>1</v>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': "The Opportunity Capgemini is seeking a Director/Sr Director level executive for an experienced ServiceNow Solution to join our solutioning team within the COE - DCX (Digital Customer experience) Practice. As a Pre-Sales Solution Consultant (also known as a 'Solutioning') for ServiceNow, you act as a trusted advisor to prospective and existing customers. Your role is to understand their business challenges and demonstrate how ServiceNow’s platform and solutions can address those needs. You work closely with the sales team to drive adoption and value realization through compelling solution presentations, demos, and proof-of-concepts."}, {'section_title': 'Key Responsibilities', 'content': 'Customer Engagement, Solution Design &amp; Demonstration, Thought Leadership, Collaboration &amp; Enablement. Conduct discovery sessions, present tailored solutions, write technical responses, estimate workload, analyze issues, communicate solutions, create demo environments, translate business requirements, stay current on product releases, provide feedback, act as SME, collaborate with teams, support marketing events, mentor junior members.'}, {'section_title': 'Ideal Candidate', 'content': 'Proven experience in pre-sales, solution consulting, or technical sales. Strong understanding of ServiceNow platform. Ability to communicate complex technical concepts. Experience with enterprise IT, cloud platforms, digital transformation. Excellent presentation and interpersonal skills. Fluent in English; additional languages a plus.'}, {'section_title': 'Preferred Qualifications', 'content': 'ServiceNow certifications (CSA, CIS). Experience in Manufacturing, Financial Services, Public Sector. Scripting languages (JavaScript). Web technologies (REST, SOAP, HTML).'}]</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Gurgaon-ServiceNow-Solutioner-Leader/1292679801/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Sales &amp; Client Management &amp; Solution Design', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1464, 'output_tokens': 730, 'total_tokens': 2194}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>426743-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>IT Disaster Recovery Consultant</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Pune-IT-Disaster-Recovery-Consultant/1378746633/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>6+ years</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore', 'IN, Bhubaneswar', 'IN, Chennai', 'IN, Coimbatore', 'IN, Gandhinagar', 'IN, Gurgaon', 'IN, Hyderabad', 'IN, Kanchipuram', 'IN, Kolkata', 'IN, Mumbai', 'IN, Navi Mumbai', 'IN, Noida', 'IN, Pune', 'IN, Salem', 'IN, Tiruchirapalli']</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>['ITSM', 'Disaster Recovery', 'DR planning', 'DR testing', 'audit', 'data analysis', 'configuration reviews', 'AWS', 'Microsoft Azure']</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-03-29T16:57:59.000Z</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>426743-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="b">
+        <v>1</v>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Develop, implement, and enhance IT Disaster Recovery processes, procedures, and documentation. Lead and coordinate end-to-end DR planning, including strategy development, scope definition, scheduling, and communication. Conduct DR tests, manage test cycles, facilitate technical team preparation, and oversee execution and post-test reporting. Communicate proactively with business owners, technical teams, and stakeholders on DR activities, business impacts, risks, and remediation plans. Prepare and deliver monthly DR reports, annual DR summaries, audit documentation, and responses to audit queries. Work closely with Customers, Delivery Managers, and Resolver Teams to determine priorities, requirements, timelines, and necessary resources.'}, {'section_title': 'Key Responsibilities', 'content': 'Coordinate DR planning, conduct DR tests, manage audit responses, prepare reports, and communicate with stakeholders.'}, {'section_title': 'Benefits', 'content': 'Flexible work arrangements, career growth programs, certifications in AWS and Microsoft Azure.'}]</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Pune-IT-Disaster-Recovery-Consultant/1378746633/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Cloud Infrastructure Management', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1295, 'output_tokens': 685, 'total_tokens': 1980}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>446902-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Design Concession Engineer</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382125533/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1-8 years</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>['airframe design', 'concession engineering', 'CATIA V5', 'metallic and composite structural components', 'structural analysis', 'Airbus standards', 'ATA57', 'engineering judgment']</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Posted 4 Days Ago</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>446902-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="b">
+        <v>1</v>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'At Capgemini Engineering, the world leader in engineering services, we bring together a global team of engineers, scientists, and architects to help the world’s most innovative companies unleash their potential. From autonomous cars to life-saving robots, our digital and software technology experts think outside the box as they provide unique R&amp;D and engineering services across all industries. Join us for a career full of opportunities. Where you can make a difference. Where no two days are the same.'}, {'section_title': 'Key Responsibilities', 'content': 'Analyze and process airframe design concessions for primary and secondary structural components. Create non-conformity assessments and evaluate NCs arising during production. Provide engineering dispositions based on structural integrity, design criteria, and Airbus standards. Design and modify machined, sheet metal, extruded, and composite parts using CATIA V5. Support SA &amp; LR programs through detailed non-conformity assessment and repair guidance. Apply engineering judgment for concession categories including T00, T100, and T200. Work in alignment with Airbus processes, standards, and documentation requirements. Collaborate with multi-functional teams to ensure compliance with ATA chapters, especially ATA 57 (wings), where applicable.'}, {'section_title': 'Benefits', 'content': 'Flexible work policies supporting work–life balance. A collaborative, inclusive environment built on engineering excellence. Access to continuous learning, aerospace domain upskilling, and global project exposure.'}]</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382125533/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Products &amp; Systems Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1670, 'output_tokens': 673, 'total_tokens': 2343}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>446901-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Design Concession Engineer</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382126633/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2-8 years</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>['airframe design', 'concession engineering', 'CATIA V5', 'metallic and composite structural components', 'aircraft structural domains', 'Airbus Standards', 'ATA57']</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Posted 4 Days Ago</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>446901-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="b">
+        <v>1</v>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'At Capgemini Engineering, the world leader in engineering services, we bring together a global team of engineers, scientists, and architects to help the world’s most innovative companies unleash their potential. From autonomous cars to life-saving robots, our digital and software technology experts think outside the box as they provide unique R&amp;D and engineering services across all industries. Join us for a career full of opportunities. Where you can make a difference. Where no two days are the same.'}, {'section_title': 'Key Responsibilities', 'content': 'Analyze and process airframe design concessions for primary and secondary structural components. Create non-conformity assessments and evaluate NCs arising during production. Provide engineering dispositions based on structural integrity, design criteria, and Airbus standards. Design and modify machined, sheet metal, extruded, and composite parts using CATIA V5. Support SA &amp; LR programs through detailed non-conformity assessment and repair guidance. Apply engineering judgment for concession categories including T00, T100, and T200. Work in alignment with Airbus processes, standards, and documentation requirements. Collaborate with multi-functional teams to ensure compliance with ATA chapters, especially ATA 57 (wings), where applicable.'}, {'section_title': 'Benefits', 'content': 'Flexible work policies supporting work–life balance. A collaborative, inclusive environment built on engineering excellence. Access to continuous learning, aerospace domain upskilling, and global project exposure.'}]</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382126633/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Products &amp; Systems Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1670, 'output_tokens': 669, 'total_tokens': 2339}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>446900-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Design Concession Engineer</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382123133/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2-6 years</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>['airframe design', 'concession engineering', 'CATIA V5', 'metallic and composite structural components', 'structural analysis', 'aircraft standards', 'ATA chapters', 'aircraft structural domains']</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Posted 8 Days Ago</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>446900-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="b">
+        <v>1</v>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'At Capgemini Engineering, the world leader in engineering services, we bring together a global team of engineers, scientists, and architects to help the world’s most innovative companies unleash their potential. From autonomous cars to life-saving robots, our digital and software technology experts think outside the box as they provide unique R&amp;D and engineering services across all industries. Join us for a career full of opportunities. Where you can make a difference. Where no two days are the same.'}, {'section_title': 'Key Responsibilities', 'content': 'Analyze and process airframe design concessions for primary and secondary structural components. Create non-conformity assessments and evaluate NCs arising during production. Provide engineering dispositions based on structural integrity, design criteria, and Airbus standards. Design and modify machined, sheet metal, extruded, and composite parts using CATIA V5. Support SA &amp; LR programs through detailed non-conformity assessment and repair guidance. Apply engineering judgment for concession categories including T00, T100, and T200. Work in alignment with Airbus processes, standards, and documentation requirements. Collaborate with multi-functional teams to ensure compliance with ATA chapters, especially ATA 57 (wings), where applicable.'}, {'section_title': 'Benefits', 'content': 'Flexible work policies supporting work–life balance. A collaborative, inclusive environment built on engineering excellence. Access to continuous learning, aerospace domain upskilling, and global project exposure.'}]</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Bangalore-Design-Concession-Engineering/1382123133/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Products &amp; Systems Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1670, 'output_tokens': 672, 'total_tokens': 2342}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>425055-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Bangalore-Software-Engineer/1382129533/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>['programming concepts', 'software design', 'software development principles', 'scientific methods', 'software engineering practice', 'team collaboration', 'problem solving']</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-04-09T11:00:58.000Z</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>425055-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="b">
+        <v>1</v>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Works in the area of Software Engineering, encompassing development, maintenance, and optimization of software solutions. Applies scientific methods, responsible for development and application of software engineering practices, supervises technical work, builds skills, and collaborates with team members.'}, {'section_title': 'Key Responsibilities', 'content': 'Develop and maintain software solutions, analyze and solve engineering problems, supervise technical and administrative tasks, collaborate with stakeholders, and deliver results with minimal supervision.'}, {'section_title': 'Benefits', 'content': ''}]</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Bangalore-Software-Engineer/1382129533/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Software Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1178, 'output_tokens': 479, 'total_tokens': 1657}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>426107-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Bangalore-Senior-Software-Engineer/1375842033/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>['software engineering', 'software development', 'software design', 'problem solving', 'team leadership', 'client interaction', 'cost management']</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Posted 6 Days Ago</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>426107-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="b">
+        <v>1</v>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Works in the area of Software Engineering which encompasses the development maintenance and optimization of software solutions and applications. Applies scientific methods to analyse and solve software engineering problems. Responsible for the development and application of software engineering practice and knowledge in research design development and maintenance. Works autonomously with minimal supervision, leads teams, and manages client needs and project issues.'}, {'section_title': 'Key Responsibilities', 'content': 'Build skills and expertise in software engineering, collaborate with team members, explain complex concepts, motivate team, and manage costs for projects.'}]</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Bangalore-Senior-Software-Engineer/1375842033/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Software Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1203, 'output_tokens': 467, 'total_tokens': 1670}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>453585-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SAP DMC Digital Manufacturing Cloud</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/job/Pune-SAP-DMC-Digital-Manufacturing-Cloud/1382140933/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Experienced Professionals</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>['IN, PUNE']</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>['Digital Manufacturing', 'SAP DMC', 'Industrial digital technologies', 'PLM', 'MES', 'Manufacturing data management', 'Engineering practice', 'Configuration', 'Deployment', 'Teamwork', 'Client interaction']</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Posted 4 Days Ago</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>453585-en_GB_SAPBTP</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="b">
+        <v>1</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'This role involves the development and application of engineering practice and knowledge in defining, configuring and deploying industrial digital technologies (including but not limited to PLM and MES) for managing continuity of information across the engineering enterprise, including design, industrialization, manufacturing and supply chain, and for managing the manufacturing data. Job Description - Grade Specific Focus on Digital Continuity and Manufacturing. Develops competency in own area of expertise. Shares expertise and provides guidance and support to others. Interprets clients needs. Completes own role independently or with minimum supervision. Identifies problems and relevant issues in straight forward situations and generates solutions. Contributes in teamwork and interacts with customers.'}]</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.capgemini.com/job/Pune-SAP-DMC-Digital-Manufacturing-Cloud/1382140933/?feedId=388633&amp;utm_source=CareerSite&amp;tcsource=apply', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Products &amp; Systems Engineering', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1052, 'output_tokens': 520, 'total_tokens': 1572}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>23204314</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Senior Analyst I ERP Package Applications</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23204314/rr-288040-sr-analyst-i-erp-package-applications-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>['SAP FICO', 'SAP FI Modules', 'SAP CO Modules', 'General Ledger', 'Accounts Receivable', 'Accounts Payable', 'Asset Accounting', 'Taxation (GST, TDS, TCS)', 'Cost Center Accounting', 'COPA', 'Product Cost Controlling', 'Internal order management', 'Profit center accounting', 'Month End and fiscal Year End Closing', 'SAP troubleshooting', 'System configuration', 'Cross-module interface setup', 'AP', 'AR', 'Asset Management', 'Integration with 3rd party software', 'Profitability Analysis', 'Cost flow', 'Revenue flow', 'Cost roll-up', 'Allocation Price Variance', 'CO summarization', 'Plan Layout', 'Product Cost Planning', 'Result Analysis', 'Revenue recognition', 'Planning &amp; budgeting']</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>23204314</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="b">
+        <v>1</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': "Job description (SAP FICO) The candidate must have worked on at least 2 full implementation projects and 1 support project. Excellent verbal and written communication skills to coordinate with the key business stakeholders, colleagues as well as OEM support partners in an appropriate/mature manner. Understanding the organization's business requirements thoroughly for smooth execution. Excellent understanding with Finance, Enterprise Structure, Global setting of organization level, Account payable and Account receivables, Automatic payment program, Banking reconciliation process, Vendor/customer master data, Asset accounting. Complete understanding of FICO integration with logistics, procurement, inventory and production, General Controlling. SAP FI Core Modules: General Ledger, Accounts Receivable, Accounts Payable, Asset Accounting, taxation (GST, TDS, TCS). SAP CO Modules: Cost Center Accounting, COPA, Product Cost Controlling, Internal order management, profit center accounting. Month End and fiscal Year End Closing activities Accounting principles, financial compliance, and process analysis. Advanced SAP troubleshooting, system configuration, and cross-module interface setup Must be able to independently handle Key uses &amp; Finance Manager, take requirements and independently provide SAP solution in terms of configuration, testing, UT &amp; IT and support issues after go-live. Preparation of Blueprint as well as implementation of the projects. Validate the reports requirements, validate any changes in customize. Provide training to end-user. Should be an expert in AP, AR and Asset Management. Expertise on an integration with 3rd party software through like; PO, BW, SD, Bâ\x80\x99One, CRM etc. Important organizational Elements of CO. Profitability Analysis (co-pa). Cost flow and revenue flow related to the profit center. Cost roll-up in product costing, Allocation Price Variance, Summarization in CO, Plan Layout, Product Cost Planning. Result Analysis /Revenue recognition with different methods like; percentage of completion. Planning &amp; budgeting forÂ costÂ objects."}]</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23204314/rr-288040-sr-analyst-i-erp-package-applications-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1455, 'output_tokens': 859, 'total_tokens': 2314}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>23196635</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Software Development Manager</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23196635/rr-0330742-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>7+ years</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>["Bachelor's degree in a relevant field"]</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>['software development', 'project management', 'software languages', 'development methodologies', 'package applications', 'technical guidance', 'quality control', 'cloud certifications', 'PMP', 'CTO', 'MBA']</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>23196635</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="b">
+        <v>1</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Manage a team responsible for package software application development. Coordinate project execution and allocate resources efficiently. Collaborate with senior management to define departmental goals. Ensure the timely delivery of software solutions. Provide technical guidance to team members. Oversee quality control and ensure adherence to coding standards. Facilitate collaboration with other departments and teams. Identify and address project risks and issues.'}, {'section_title': 'Key Responsibilities', 'content': 'Manage a team responsible for package software application development. Coordinate project execution and allocate resources efficiently. Collaborate with senior management to define departmental goals. Ensure the timely delivery of software solutions. Provide technical guidance to team members. Oversee quality control and ensure adherence to coding standards. Facilitate collaboration with other departments and teams. Identify and address project risks and issues.'}, {'section_title': 'Benefits', 'content': 'At DXC Technology, we believe strong connections and community are key to our success. Our work model prioritizes in-person collaboration while offering flexibility to support wellbeing, productivity, individual work styles, and life circumstances. We’re committed to fostering an inclusive environment where everyone can thrive.'}]</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23196635/rr-0330742-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Software Development', 'qualifications': ["Bachelor's degree in a relevant field"]}</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1299, 'output_tokens': 574, 'total_tokens': 1873}</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>23123606</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Senior Analyst I Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23123606/rr-0329892-sr-analyst-i-infrastructure-services-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>['Active Directory', 'Domain Controllers', 'OU management', 'Group Policy (GPO)', 'DNS', 'DHCP', 'Kerberos', 'NTLM', 'LDAP', 'Single Sign-On (SSO)', 'ADFS', 'SAML', 'federation technologies', 'Azure Active Directory (Azure AD / Entra ID)', 'PowerShell', 'Windows Server', 'Windows client operating systems', 'identity and access management']</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>23123606</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="b">
+        <v>1</v>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Key Responsibilities: Administer and support Active Directory infrastructure, manage authentication mechanisms, implement SSO solutions, manage Azure AD services, develop PowerShell scripts, troubleshoot identity issues, collaborate with security teams, ensure security compliance.'}, {'section_title': 'Key Responsibilities', 'content': 'Administer and support Active Directory infrastructure, manage authentication mechanisms, implement SSO solutions, manage Azure AD services, develop PowerShell scripts, troubleshoot identity issues, collaborate with security teams, ensure security compliance.'}, {'section_title': 'Benefits', 'content': 'Our work model prioritizes in-person collaboration while offering flexibility to support wellbeing, productivity, individual work styles, and life circumstances. We foster an inclusive environment.'}]</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23123606/rr-0329892-sr-analyst-i-infrastructure-services-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Information Technology', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1247, 'output_tokens': 546, 'total_tokens': 1793}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>23079040</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Services Analyst</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23079040/sr-analyst-i-infrastructure-services-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>["Bachelor's degree in a relevant field"]</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>['Infrastructure support', 'Troubleshooting', 'Infrastructure project implementation', 'Documentation', 'Technical support', 'Data analysis', 'Problem-solving', 'Certifications (Cisco CCNA, AWS, CompTIA Security+)']</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>23079040</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="b">
+        <v>1</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Provide expert technical support in infrastructure services, respond to complex issues, assist in infrastructure project implementation, monitor and troubleshoot systems, collaborate to improve efficiency, develop documentation, apply deep technical knowledge, follow best practices, and apply critical thinking.'}, {'section_title': 'Key Responsibilities', 'content': 'Support infrastructure systems, troubleshoot issues, implement projects, develop documentation, collaborate with team, apply technical knowledge, follow standards.'}, {'section_title': 'Qualifications', 'content': "Bachelor's degree or equivalent, 5+ years relevant experience, certifications preferred."}]</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23079040/sr-analyst-i-infrastructure-services-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': 'Information Technology', 'qualifications': ["Bachelor's degree in a relevant field"]}</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1319, 'output_tokens': 468, 'total_tokens': 1787}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>23071944</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Associate Manager Scrum Master</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23071944/associate-manager-scrum-master-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>['Scrum', 'Agile', 'Project Management', 'Team Leadership']</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>23071944</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="b">
+        <v>1</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'Assosiate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum MasterAssociate Manager Scrum Master...'}, {'section_title': 'About DXC Technology', 'content': 'At DXC Technology, we believe strong connections and community are key to our success. Our work model prioritizes in-person collaboration while offering flexibility to support wellbeing, productivity, individual work styles, and life circumstances. We’re committed to fostering an inclusive environment where everyone can thrive.'}, {'section_title': 'Recruitment Fraud Warning', 'content': 'Recruitment fraud is a scheme in which fictitious job opportunities are offered to job seekers typically through online services, such as false websites, or through unsolicited emails claiming to be from the company. These emails may request recipients to provide personal information or to make payments as part of their illegitimate recruiting process. DXC does not make offers of employment via social media networks and DXC never asks for any money or payments from applicants at any point in the recruitment process, nor ask a job seeker to purchase IT or other equipment on our behalf.'}]</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23071944/associate-manager-scrum-master-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 2125, 'output_tokens': 521, 'total_tokens': 2646}</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>23049516</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>EPS Senior Technical Engineer</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23049516/eps-senior-technical-engineer-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>['Switch systems', 'Base24 EPS', 'configuration', 'scripting', 'SDK', 'Australian and scheme compliance', 'card schemes', 'interfacing', 'programming', 'C++', 'Java', 'Linux', 'VMware', 'cloud systems (Azure, AWS)', 'ISO 8583', 'XML', 'VISA', 'MasterCard', 'Amex', 'JCB']</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>23049516</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="b">
+        <v>1</v>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'Senior Technical engineer BASE24 EPS Job Location: Bangalore Job Details: To develop, test, and deploy fit-for-purpose software solutions. This includes CSMs on BASE 24 EPS. To configure the BASE24 EPS modules as per the requirements. To prepare migration scripts. To configure the interchange specifications like VISA, MasterCard, AMEX, JCB. This includes the periodical mandates, updates, test. To customise, configure the interfaces. This includes testing, fixing the issues. To configure terminals, ATMs and interfaces. To configure, test various host systems. To configure various security keys for the interchanges, terminals, cards and PVKs. To configure and integrate BASE24 EPS with HSMs. To generate required MIS/reports as per business requirements.'}, {'section_title': 'Key Responsibilities', 'content': ''}, {'section_title': 'Benefits', 'content': ''}]</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23049516/eps-senior-technical-engineer-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1504, 'output_tokens': 569, 'total_tokens': 2073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>22666501</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Senior BASE24 EPS Support</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22666501/senior-base24-eps-support-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>4-8 years</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>['Base24-eps', 'ACI Base24-eps', 'ISO 8583', 'payment systems', 'application support', 'troubleshooting', 'diagnosing transaction failures', 'system outages', 'payment networks', 'ATM/POS/Ecom systems', 'support', 'integration processes']</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>22666501</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="b">
+        <v>1</v>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description', 'content': 'Experience 4 to 8 years of hands-on support experience with ACI Base24-eps applications. Proven track record in application support roles within the cards and payments domain. Key Responsibilities Monitor, troubleshoot, and resolve issues in Base24-eps payment systems. Act as the first responder for production issues, ensuring minimal downtime. Diagnose and resolve transaction failures, ISO 8583 message issues, and system outages. Handle transaction failures, outages, and performance issues with a structured problem-solving approach. Support integration of Base24-eps with other bank systems and external card schemes. Collaborate across teams, clearly explaining technical issues to stakeholders. Maintain and support payment networks, ATM/POS/Ecom systems, and settlement processes.'}, {'section_title': 'Skills &amp; Competencies', 'content': 'In-depth knowledge of ISO 8583 messaging systems. Strong analytical, debugging, and problem-solving skills. Experience with Base24-eps modules and integration processes. Good understanding of payment networks, ATM/POS/Ecom systems, and settlement workflows. Ability to work effectively in a 24x7 support model.'}, {'section_title': 'Additional Information', 'content': 'At DXC Technology, we believe strong connections and community are key to our success. Our work model prioritizes in-person collaboration while offering flexibility to support wellbeing, productivity, individual work styles, and life circumstances. We’re committed to fostering an inclusive environment where everyone can thrive. Recruitment fraud is a scheme in which fictitious job opportunities are offered to job seekers typically through online services, such as false websites, or through unsolicited emails claiming to be from the company. These emails may request recipients to provide personal information or to make payments as part of their illegitimate recruiting process. DXC does not make offers of employment via social media networks and DXC never asks for any money or payments from applicants at any point in the recruitment process, nor ask a job seeker to purchase IT or other equipment on our behalf. More information on employment scams is available here.'}]</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22666501/senior-base24-eps-support-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1270, 'output_tokens': 761, 'total_tokens': 2031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>23024388</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Manager Solution Architecture</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/23024388/manager-solution-architecture-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>['IN, Gurgaon']</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>['Microsoft Power Platform', 'Power Apps', 'Power Automate', 'Power BI', 'Copilot Studio', 'Google AppSheet', 'ServiceNow', 'AI technologies', 'Solution Design', 'Event Hosting', 'Project Management', 'Pre-sales', 'Communication Skills']</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>23024388</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="b">
+        <v>1</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': "The Solution Architect will be responsible for designing and delivering scalable, innovative solutions using Microsoft Power Platform, Google AppSheet, ServiceNow, and AI technologies. Working closely with L'Oreal platform CoE team and enterprise architect team for the technical direction and governance."}, {'section_title': 'Key Responsibilities', 'content': 'Solution Design &amp; Architecture, Design integrations, Analyze business needs, translate requirements, create presentations, event hosting, stakeholder engagement, project management, change management, drive citizen development culture.'}, {'section_title': 'Benefits', 'content': 'Flexible work model, inclusive environment, community focus.'}]</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/23024388/manager-solution-architecture-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1549, 'output_tokens': 465, 'total_tokens': 2014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>22666467</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Base 24 Quality Engineer/Lead</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://careers.dxc.com/job/22666467/base-24-quality-engineer-lead-gurgaon-in/</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>['IN, Bangalore']</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>['test case creation', 'test management tools', 'quality assurance', 'Switch testing', 'payment systems', 'transaction switch', 'e-commerce', 'certifications (VISA, MasterCard, Amex, JCB)', 'simulators', 'automated testing tools', 'JIRA']</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>22666467</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="b">
+        <v>1</v>
+      </c>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>[{'section_title': 'Job Description Summary', 'content': 'Base 24 Quality Engineer/Lead Job Location: Bangalore. 5+ years of experience in developing, creating, prioritizing, and organizing test cases for web/mobile applications. Familiarity with defect tracking systems and test management tools. Experience in quality assurance of issuing business payments and cards. Specific experience in Switch testing (BASE24, BAE24 EPS, ACI UPF) is desirable. Domain understanding of payments, issuing, transaction switch, latest payment systems, e-commerce. Experience in QA on issuing products, certifications of interchanges like VISA, MasterCard, Amex, JCB. Conducting QA testing through simulators and mock environments. Understanding of automated testing tools and management tools like JIRA.'}]</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>{'url': 'https://careers.dxc.com/job/22666467/base-24-quality-engineer-lead-gurgaon-in/', 'strategy': 'html', 'site_type': 'CUSTOM_API', 'department': '', 'qualifications': []}</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 1302, 'output_tokens': 490, 'total_tokens': 1792}</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>744000119376307</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Unit Assembler, 2nd Shift</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119376307</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Previous experience in assembly or manufacturing preferred</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>['Norman, United States']</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>['Strong manual dexterity', 'Ability to read and interpret assembly instructions and blueprints', 'Basic math skills', 'Proficiency in using hand tools and power tools', 'Knowledge of quality control procedures', 'Attention to detail', 'Physical ability to stand for extended periods and lift up to 50 pounds', 'Teamwork and communication skills', 'Workplace safety and efficiency']</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>744000119376307</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="b">
+        <v>1</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Manual dexterity', 'Reading blueprints', 'Quality control'], 'tools_and_technologies': ['Hand tools', 'Power tools'], 'certifications': [], 'soft_skills': ['Attention to detail', 'Teamwork', 'Communication'], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>744000119374573</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Unit Assembler, 1st Shift</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119374573</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Previous experience in assembly or manufacturing preferred</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>['Norman, United States']</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>['Strong manual dexterity', 'Ability to read and interpret assembly instructions and blueprints', 'Basic math skills', 'Proficiency in using hand tools and power tools', 'Knowledge of quality control procedures', 'Attention to detail', 'Physical ability to stand and lift up to 50 pounds', 'Strong teamwork and communication skills', 'Commitment to safety and efficiency']</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>744000119374573</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="b">
+        <v>1</v>
+      </c>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>['Work hours: 1st shift', 'Job responsibilities include assembly, quality checks, safety adherence, and continuous improvement']</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Manual dexterity', 'Blueprint reading', 'Quality control'], 'tools_and_technologies': ['Hand tools', 'Power tools'], 'certifications': [], 'soft_skills': ['Teamwork', 'Communication', 'Attention to detail'], 'inferred_skills': ['Manufacturing experience', 'Safety awareness'], 'benefits': ['Equal Opportunity Employer', 'Workplace safety']}</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 250, 'total_tokens': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>744000119283547</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>APAC Physical Logistics, Project Business Analyst</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119283547</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>['APAC']</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>['logistics', 'data analysis', 'supply chain', 'Power BI', 'Tableau', 'Excel', 'stakeholder collaboration']</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>744000119283547</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="b">
+        <v>1</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['logistics', 'data analysis', 'supply chain', 'Power BI', 'Tableau', 'Excel'], 'tools_and_technologies': ['Power BI', 'Tableau', 'Excel'], 'certifications': [], 'soft_skills': ['analytical thinking', 'stakeholder collaboration', 'communication'], 'inferred_skills': ['project management', 'data visualization'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>744000119186647</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Customer Service Associate</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119186647</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Previous customer service experience preferred</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>['Norristown, United States']</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>['Excellent verbal and written communication skills', 'Strong problem-solving abilities', 'Attention to detail', 'Proficiency in customer service software and CRM systems', 'Basic computer skills, including Microsoft Office', 'Ability to multitask and prioritize', 'Patient and empathetic approach']</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>744000119186647</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="b">
+        <v>1</v>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['Respond to customer inquiries via phone, email, and chat', 'Assist with product information, order processing, and account management', 'Resolve customer complaints with empathy and efficiency', 'Maintain records of interactions and transactions', 'Collaborate with departments', 'Identify and escalate complex issues', 'Stay updated on products, services, and policies', 'Support colleagues and contribute to team environment']</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service experience', 'Communication skills', 'Problem-solving'], 'tools_and_technologies': ['Customer service software', 'CRM systems', 'Microsoft Office'], 'certifications': [], 'soft_skills': ['Empathy', 'Patience', 'Teamwork'], 'inferred_skills': ['Multitasking', 'Prioritization'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>744000119127010</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HVAC Technician III</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119127010</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Desejável experiência em manutenções preventivas e corretivas de equipamento de pequeno porte</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>['São Paulo']</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Ensino completo em Técnico de Refrigeração - Ar condicionado</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>['Refrigeração', 'Eletrica', 'Eletrônica', 'Mecânica', 'Solda', 'Conhecimento básico em informática']</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>744000119127010</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="b">
+        <v>1</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>['Descrição da empresa', 'Descrição do emprego', 'Qualificações', 'Informações Adicionais']</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['Softwares de atualização de sistemas VRF, Chiller Scroll e Parafuso'], 'certifications': ['Técnico em Refrigeração, Ar Condicionado ou correlatos'], 'soft_skills': ['Comprometimento', 'Segurança', 'Trabalho em equipe', 'Organização'], 'inferred_skills': ['Manutenção preventiva e corretiva', 'Instalação de sistemas HVAC', 'Inspeção de rotinas diárias'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub (Gympass)', 'Assistência psicológica, social, jurídica e financeira', 'Licença-maternidade e paternidade estendida', 'KIT parentalidade', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/ SESI']}</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 150, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>744000119125048</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Técnico de HVAC III</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119125048</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Experiência prática em instalação, manutenção e reparo de sistemas de climatização</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>['Manaus, Brasil']</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Licença ou certificação válida em HVAC (ou qualificação equivalente reconhecida no Brasil)</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>['Operar Sistema de Ar Condicionado Central', 'Instalar equipamentos diversos', 'Realizar pequenos serviços de soldas', 'Manutenção corretiva e preventiva no sistema mecânico de refrigeração', 'Utilizar veículo da empresa', 'Seguir normas técnicas e de segurança', 'Conhecimento básico em eletrônica', 'Realizar start-up de equipamentos', 'Atualização de softwares', 'Recolhimento de fluídos refrigerantes', 'Limpeza do sistema com 141B ou similar', 'Pressurização com nitrôgeno', 'Instalar e substituir peças', 'Substituir selo mecânico', 'Executar overhaul em campo Hitachi', 'Diagnóstico e manutenção em mancais magnéticos e equipamentos de absorção', 'Análise de vibração']</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Remoto/Híbrido</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>744000119125048</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="b">
+        <v>1</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>['Descrição da empresa', 'Descrição do emprego', 'Qualificações', 'Informações Adicionais']</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Otimização de eficiência energética', 'Programação de sistemas', 'Manutenção preventiva', 'Gestão de estoque'], 'tools_and_technologies': ['Equipamentos de diagnóstico', 'Ferramentas de teste específicas', 'Softwares de atualização'], 'certifications': ['Certificação em HVAC reconhecida no Brasil'], 'soft_skills': ['Habilidades analíticas', 'Resolução de problemas', 'Habilidades organizacionais', 'Comunicação eficaz'], 'inferred_skills': ['Capacidade de trabalhar em equipe', 'Capacidade de trabalhar sob pressão'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub (Gympass)', 'Assistência psicológica, social, jurídica e financeira', 'Licença-maternidade e paternidade estendida', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/ SESI']}</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>744000119121787</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Analista de Planejamento de Serviços JR</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119121787</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>['Brazil']</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Ensino superior em andamento, nas áreas administrativas e áreas correlatas</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>['Planejamento de manutenção', 'Controle de backlog de serviços', 'Elaboração de relatórios de indicadores', 'Gestão de fornecedores', 'Controle de escopo técnico']</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>744000119121787</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="b">
+        <v>1</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['Descrição da empresa', 'Descrição do emprego', 'Qualificações', 'Informações Adicionais']</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Gestão de projetos', 'Análise de dados', 'Comunicação eficaz'], 'tools_and_technologies': ['Microsoft Office', 'Sistemas de gestão de manutenção'], 'certifications': ['Certificação em manutenção industrial', 'Certificação em gestão de projetos'], 'soft_skills': ['Organização', 'Proatividade', 'Trabalho em equipe'], 'inferred_skills': ['Capacidade analítica', 'Resolução de problemas'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub (Gympass)', 'Assistência psicológica, social, jurídica e financeira', 'Licença-maternidade e paternidade estendida', 'KIT parentalidade', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/ SESI']}</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>744000119014967</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Coil Utility Assembler, 2nd shift</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119014967</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>On job training</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>['Not specified']</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>['Ability to read and interpret blueprints', 'Use of decimals, fractions and scales', 'Basic computer operating skills', 'Ability to work 2nd shift']</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>744000119014967</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M230" t="b">
+        <v>1</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['Work Safe!', 'Perform visual inspections', 'Rework or minor repairs', 'Housekeeping functions', 'Maintain tools and work area', 'Participate in safety and environmental training']</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['MES', 'blueprints', 'measuring tape'], 'certifications': [], 'soft_skills': ['Attention to detail', 'Safety consciousness'], 'inferred_skills': ['Assembly skills', 'Mechanical aptitude'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>744000119014907</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Coil Utility Assembler II, 1st shift</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119014907</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Entry-level</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>['Unknown']</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>['Basic computer operating skills', 'Ability to read and interpret blueprints', 'Use of decimals, fractions and scales', 'Physical ability to lift up to 50 pounds', 'Repetitive hand and arm movements', 'Attention to detail']</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>744000119014907</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M231" t="b">
+        <v>1</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['Work safety and environmental practices', 'Use of PPE', 'Housekeeping and organization', 'Rework and minor repairs']</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['MES', 'blueprints', 'measuring tools'], 'certifications': [], 'soft_skills': ['attention to detail', 'safety consciousness'], 'inferred_skills': ['assembly', 'inspection', 'repair'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>744000119014807</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Machine Operator III, 1st Shift</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119014807</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>['Not specified']</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>['Basic computer operating skills', 'Ability to read and interpret blueprints', 'Use of decimals, fractions and scales', 'Complete in plant Brazer training course', 'On job training']</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>744000119014807</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M232" t="b">
+        <v>1</v>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>['Operate press machine to fabricate sheet metal parts', 'Inspect parts and operate material transfer system', 'Set dials on control console for automatic shears', 'Perform calculations for manual shear blade position', 'Maintain machine, equipment, and work area', 'Follow safety and environmental practices']</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['Press machine', 'MES system', 'Control console', 'Manual shear'], 'certifications': ['In plant Brazer training'], 'soft_skills': ['Attention to detail', 'Safety consciousness', 'Ability to perform repetitive tasks'], 'inferred_skills': ['Mechanical aptitude', 'Physical stamina'], 'benefits': ['Equal Opportunity Employer', 'Safety and environmental training']}</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 370, 'output_tokens': 70, 'total_tokens': 440}</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>744000119014767</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Unit Assembler, 2nd Shift</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000119014767</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>['Norman, United States']</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>['Manual dexterity', 'Ability to read and interpret assembly instructions and blueprints', 'Basic math skills', 'Proficiency with hand tools and power tools', 'Knowledge of quality control procedures', 'Attention to detail', 'Physical ability to stand and lift up to 50 pounds', 'Teamwork and communication skills', 'Workplace safety awareness']</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>744000119014767</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="b">
+        <v>1</v>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>['Work hours: 2nd shift', 'Physical requirements: stand for extended periods, lift up to 50 pounds', 'Preferred experience: assembly or manufacturing', 'Work environment: fast-paced production']</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Assembly experience', 'Manufacturing background'], 'tools_and_technologies': ['Hand tools', 'Power tools', 'Assembly equipment'], 'certifications': [], 'soft_skills': ['Teamwork', 'Communication', 'Attention to detail', 'Safety consciousness'], 'inferred_skills': ['Quality control', 'Process improvement'], 'benefits': ['Equal Opportunity Employer', 'Workplace safety']}</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 250, 'total_tokens': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>744000118877667</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HVAC Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118877667</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>['Birmingham, United States']</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent; HVAC certification preferred</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>['Knowledge of HVAC systems, components, and industry best practices', 'Customer service skills', 'Sales experience', 'Proficiency in POS and inventory management software', 'Basic math skills', 'Knowledge of local building codes and regulations', 'Strong communication and interpersonal skills', 'Organizational skills', 'Flexibility to work weekends and evenings']</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>744000118877667</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="b">
+        <v>1</v>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service', 'Sales', 'HVAC knowledge'], 'tools_and_technologies': ['POS systems', 'Inventory management software'], 'certifications': ['HVAC certification'], 'soft_skills': ['Communication', 'Interpersonal skills', 'Organizational skills', 'Detail-oriented'], 'inferred_skills': [], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>744000118231788</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Quality Management System Engineer</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118231788</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>3+ years</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>['Wichita, United States']</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>['Quality management system standards (ISO 9001, ISO 13485, AS9100)', 'Root cause analysis', 'Corrective and preventive action (CAPA)', 'Audit procedures and compliance documentation', 'Process improvement methodologies (Lean, Six Sigma, Kaizen)', 'Data analysis tools and statistical software', 'Failure mode and effects analysis (FMEA)', 'Risk management frameworks', 'ERP or MES familiarity', 'Technical writing', 'Project management', 'Communication and interpersonal skills']</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>744000118231788</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="b">
+        <v>1</v>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Certification in quality management (ASQ CQE, CQA)', 'ISO 9001:2015 Lead Auditor', 'Experience in regulated industries (aerospace, automotive, medical devices, pharmaceuticals)'], 'tools_and_technologies': ['Statistical software', 'ERP', 'MES'], 'certifications': ['ASQ CQE', 'CQA', 'ISO 9001:2015 Lead Auditor'], 'soft_skills': ['Organizational skills', 'Project management', 'Effective communication', 'Collaboration'], 'inferred_skills': [], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>744000118230815</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Equipment Calibration Technician</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118230815</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>['Wichita, United States']</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>['Calibration procedures', 'Precision measurement tools', 'Troubleshooting', 'Technical documentation', 'Quality assurance standards', 'Calibration standards (ISO 17025, NIST)']</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>744000118230815</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="b">
+        <v>1</v>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Data analysis', 'Statistical process control', 'Preventive maintenance', 'Experience in regulated industries'], 'tools_and_technologies': ['Digital multimeters', 'Pressure gauges', 'Thermometers', 'Specialized testing devices'], 'certifications': ['ISO 17025', 'NIST standards'], 'soft_skills': ['Organizational skills', 'Attention to detail', 'Problem-solving', 'Collaboration'], 'inferred_skills': [], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>744000118226618</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Técnico de HVAC I</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118226618</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1 a 2 anos</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>['Hortolândia']</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Formação técnica completa na área de HVAC, Refrigeração, Eletrotécnica, Mecânica ou correlatas</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>['Instalação de sistemas HVAC', 'Manutenção preventiva e corretiva', 'Diagnóstico de falhas em sistemas HVAC', 'Leitura e interpretação de projetos técnicos', 'Normas técnicas e regulamentos de segurança', 'Familiaridade com ferramentas e equipamentos especializados', 'Conhecimentos básicos de informática', 'Carteira de habilitação válida', 'Fluência em português e inglês intermediário', 'Habilidades de comunicação e atendimento ao cliente']</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>744000118226618</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="b">
+        <v>1</v>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>['Responsabilidades principais', 'Qualificações', 'Informações adicionais']</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Diagnóstico de problemas', 'Leitura de esquemas elétricos', 'Atendimento ao cliente'], 'tools_and_technologies': ['Ferramentas de instalação e manutenção HVAC', 'Sistemas de registro e comunicação'], 'certifications': ['Certificação em HVAC'], 'soft_skills': ['Proatividade', 'Organização', 'Comunicação eficaz', 'Trabalho em equipe'], 'inferred_skills': ['Capacidade de atuar sob pressão', 'Comprometimento com normas de segurança'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub', 'Programa de Apoio ao Empregado', 'Licença-maternidade e paternidade estendida', 'KIT parentalidade', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/ SESI']}</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>744000118176097</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118176097</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2-4 years</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>['East Granby, CT']</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>High School diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Interpersonal skills', 'Communication skills', 'Organizational skills', 'Teamwork', 'Analytical skills', 'Problem-solving', 'Proficiency with Windows and Microsoft Office', 'Cash handling', 'Point-of-sale (POS) systems']</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>744000118176097</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>USD 22.00 - USD 25.00 hourly</t>
+        </is>
+      </c>
+      <c r="M238" t="b">
+        <v>1</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>['Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Experience in HVAC, industrial, or manufacturing sales', 'Knowledge of inventory management systems', 'Warehouse operations', 'Forklift certification', 'CRM software experience'], 'tools_and_technologies': ['Microsoft Office', 'POS systems', 'CRM software'], 'certifications': ['Forklift certification'], 'soft_skills': ['Customer relationship management', 'Empathy', 'Professionalism', 'Attention to detail', 'Time management'], 'inferred_skills': ['Sales promotion', 'Order processing', 'Inventory management', 'Customer follow-up', 'Problem resolution'], 'benefits': ['Career development', 'Collaborative environment', 'Safety protocols']}</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>744000118175958</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Driver / Warehouse</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118175958</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2+ years as a delivery driver, 1+ year in warehouse environment</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>['Westbrook, United States']</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>["Valid driver's license with a clean driving record", 'Forklift certification', 'Physical ability to lift and move heavy items', 'Strong attention to detail', 'Excellent time management and organizational skills']</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>744000118175958</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>USD 23 - USD 25 hourly</t>
+        </is>
+      </c>
+      <c r="M239" t="b">
+        <v>1</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Strong interpersonal and customer relationship skills', 'Effective written and verbal communication', 'Teamwork skills', 'Analytical and problem-solving capabilities', 'Proficiency in Windows and Microsoft Office', 'Familiarity with inventory management systems'], 'tools_and_technologies': ['Material handling equipment', 'Forklifts', 'Inventory management systems', 'Microsoft Office'], 'certifications': ['Forklift certification'], 'soft_skills': ['Customer-focused', 'Detail-oriented', 'Collaborative', 'Flexible', 'Efficient'], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>744000118175324</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sound and Vibration Engineer</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000118175324</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>['Norman, OK']</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Bachelor’s or Master’s degree in Acoustics, Mechanical Engineering, or a related discipline</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>['Proficiency with acoustic measurement and analysis software', 'Skilled in vibration measurement and diagnostic tools', 'Strong understanding of HVAC components, systems, and processes', 'In-depth knowledge of mechanical noise and vibration sources, transmission paths, and isolation techniques', 'Familiarity with industry rating and test standards, including AHRI, ASHRAE, AMCA International, ISO, ANSI, and ASTM', 'Excellent analytical and problem-solving abilities', 'Strong project management skills', 'Effective written and verbal communication skills', 'Ability to work independently and within a team environment', 'Willingness to travel occasionally']</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>744000118175324</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="b">
+        <v>1</v>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>['Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['Acoustic measurement and analysis software', 'Vibration measurement and diagnostic tools'], 'certifications': ['AHRI', 'ASHRAE', 'AMCA International', 'ISO', 'ANSI', 'ASTM'], 'soft_skills': ['Analytical thinking', 'Problem-solving', 'Project management', 'Communication skills'], 'inferred_skills': ['Research and development', 'Standards compliance', 'Technical documentation'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 350, 'total_tokens': 600}</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>744000117733025</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Delivery Driver - Warehouse Coordinator</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000117733025</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>4-6 years of warehouse operations experience</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>High School diploma or equivalent combined education and experience</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>['Warehouse operations', 'Customer relationship management', 'Decision-making', 'Communication skills', 'Teamwork', 'Analytical skills', 'Forklift operation', 'RF inventory management', 'Proficiency in Windows and Microsoft Office']</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>744000117733025</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="b">
+        <v>1</v>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Warehouse management', 'Customer service', 'Inventory control'], 'tools_and_technologies': ['RF barcode systems', 'Microsoft Office Suite'], 'certifications': ['Forklift certification (desired)'], 'soft_skills': ['Interpersonal skills', 'Organization', 'Decision-making', 'Teamwork'], 'inferred_skills': ['Safety compliance', 'Inventory management', 'Customer communication'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>744000117733907</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Warranty Specialist 1</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000117733907</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>['Wichita, United States']</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Warranty processing', 'SAP', 'Microsoft Office (Word, Excel, Outlook)', 'Analytical skills', 'Problem-solving', 'Organizational skills', 'Communication skills in English', 'Bilingual in English/Spanish (preferred)']</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>744000117733907</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Competitive, based on experience</t>
+        </is>
+      </c>
+      <c r="M242" t="b">
+        <v>1</v>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>['Benefits include health coverage, 401(k), paid time off, parental leave, life and disability protection.']</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Report generation', 'Data analysis', 'Warranty policies', 'Claims systems'], 'tools_and_technologies': ['SAP', 'Microsoft Office'], 'certifications': [], 'soft_skills': ['Customer focus', 'Empathy', 'Professional communication', 'Team collaboration'], 'inferred_skills': ['Attention to detail', 'Multitasking', 'Adaptability'], 'benefits': ['Health insurance', 'Retirement plan', 'Paid time off', 'Parental leave', 'Life and disability insurance']}</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>744000117388447</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000117388447</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2+ years of retail or customer service experience</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>['Jackson, TN']</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Point of Sale (POS) operation', 'Product knowledge', 'Cash handling', 'Communication skills', 'Math skills', 'Teamwork', 'Problem-solving', 'Inventory management', 'Physical stamina']</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>744000117388447</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="b">
+        <v>1</v>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>['Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Forklift certification'], 'tools_and_technologies': ['Point of Sale (POS) systems'], 'certifications': ['Forklift certification (training provided)'], 'soft_skills': ['Customer engagement', 'Empathy', 'Team collaboration', 'Problem-solving', 'Attention to detail'], 'inferred_skills': ['Multitasking', 'Physical endurance', 'Time management'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>744000117327098</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Facilities Engineer</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000117327098</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Minimum of 5 years in facilities engineering or management</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in mechanical, Electrical, Civil Engineering, Facilities Management, or a related field</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>['Building systems knowledge (HVAC, electrical, plumbing)', 'Project management', 'Budget oversight', 'Safety standards and building codes', 'Problem-solving and analytical skills', 'Organizational skills']</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>744000117327098</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Competitive salary</t>
+        </is>
+      </c>
+      <c r="M244" t="b">
+        <v>1</v>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>['Benefits include health coverage, 401(k), paid time off, parental leave, life and disability protection']</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Professional Engineer (PE) license', 'Building Management Systems (BMS)', 'Computerized Maintenance Management Systems (CMMS)', 'CAD software proficiency', 'HVAC manufacturing experience'], 'tools_and_technologies': ['BMS', 'CMMS', 'CAD'], 'certifications': ['PE', 'CFM', 'IFMA', 'LEED'], 'soft_skills': ['Problem-solving', 'Organizational skills', 'Attention to detail'], 'inferred_skills': ['Facility planning', 'Energy management', 'Safety compliance'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability insurance']}</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>744000116684977</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Staff Controls Engineer</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000116684977</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Minimum of 6 years</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>['North America']</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Bachelor's degree BS or Masters in Electrical, Mechanical, or Controls Engineering</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>['Programming experience with embedded controls or PLCs', 'Troubleshooting complex control systems', 'Strong communication and interpersonal skills', 'Knowledge of industry standards and regulations related to HVAC systems', 'Ability to manage multiple projects']</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Occasional travel for on-site support and system installations</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>744000116684977</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="b">
+        <v>1</v>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>['Job Duties', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC products or Building Automation experience'], 'tools_and_technologies': ['High-level software tools', 'Embedded controls', 'PLCs'], 'certifications': [], 'soft_skills': ['Effective collaboration', 'Teamwork', 'Communication'], 'inferred_skills': ['Control system design', 'Simulation and testing', 'Technical documentation'], 'benefits': ['Premium health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>744000116665467</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sr Staff Engineer Heat Pumps and Advanced Systems</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000116665467</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>8 years</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>['Wichita, KS']</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Mechanical Engineering, Electrical Engineering, or a related field</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>['Design of variable speed compression systems', 'Inverter technology', 'HVAC system design', 'Industry standards (AHRI, ASHRAE, DOE, EPA, NEC, UL, CSA)', 'HVAC unit wiring', 'Algorithm development', 'Instrumentation', 'Vapor injection refrigeration system designs', 'Utilizing FMEAs for product lifecycle design']</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>No Telecommuting Allowed</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>744000116665467</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="b">
+        <v>1</v>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['Vapor injection', 'Remote Viewer', 'Variable Capacity Control', 'HVAC equipment', 'Inverter technology'], 'certifications': ['AHRI', 'ASHRAE', 'DOE', 'EPA', 'NEC', 'UL', 'CSA'], 'soft_skills': ['Collaboration', 'Project management', 'Problem-solving', 'Communication'], 'inferred_skills': ['System analysis', 'Prototyping', 'Testing and validation', 'Process development'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>744000116261017</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Warehouse and Logistics Supervisor</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000116261017</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>3+ years of warehouse operations or logistics management experience</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>['Wichita, Kansas']</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>['Proficiency with warehouse management systems (WMS) and inventory management software', 'Strong knowledge of logistics operations, supply chain processes, and inventory control procedures', 'Solid understanding of safety regulations, OSHA compliance, and workplace safety best practices', 'Excellent organizational and time management skills', 'Strong analytical and problem-solving abilities', 'Proficient in Microsoft Office applications and data analysis', 'Excellent communication and interpersonal skills', 'Ability to work in a fast-paced environment and adapt to changing priorities', 'Forklift certification or willingness to obtain certification', 'Experience with shipping and receiving operations', 'Familiarity with lean or continuous improvement methodologies', 'Extended MRP and/or ERP experience']</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>744000116261017</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="b">
+        <v>1</v>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>['Company Description', 'Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Forklift certification', 'Shipping and receiving operations', 'Lean or continuous improvement methodologies', 'Extended MRP and/or ERP'], 'tools_and_technologies': ['Warehouse management systems (WMS)', 'Inventory management software', 'Microsoft Office'], 'certifications': ['Forklift certification'], 'soft_skills': ['Organizational skills', 'Time management', 'Communication skills', 'Interpersonal skills', 'Problem-solving'], 'inferred_skills': ['Leadership', 'Safety compliance', 'Process optimization'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 350, 'total_tokens': 600}</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>744000115760657</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>CS Ducted</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115760657</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Minimum of 1 year of customer service experience, preferably in a manufacturing environment</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Business or a related field, or equivalent experience</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Communication skills', 'Problem-solving', 'Detail-oriented', 'Prioritization']</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>744000115760657</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="b">
+        <v>1</v>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>['Enter and accurately process customer orders through the relevant systems', 'Provide timely updates and confirmation to customers regarding their orders', 'Coordinate with sales, supply chain, and back-office teams to resolve any issues', 'Monitor order status and manage pending orders effectively', 'Address and resolve customer complaints promptly and professionally']</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service', 'Communication skills', 'Problem-solving'], 'tools_and_technologies': ['Order processing systems'], 'certifications': [], 'soft_skills': ['Attention to detail', 'Effective communication', 'Problem resolution'], 'inferred_skills': ['Time management', 'Team coordination'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>744000115711378</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Técnico HVAC Especialista - Região Sul (Paraná/Santa Catarina e Rio Grande do Sul)</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115711378</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Experiência em manutenções preventivas e corretivas de equipamento de grande porte</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>['Paraná', 'Santa Catarina', 'Rio Grande do Sul']</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Formação Técnica, Superior cursando em Mecânica ou correlatos (Eletrônica, Elétrica, Eletrôtecna ou automação)</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>['Refrigeração', 'Eletrica', 'Eletrônica', 'Mecânica', 'Solda', 'Conhecimento básico em informática']</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>744000115711378</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="b">
+        <v>1</v>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>['Benefícios: PLR, Plano de Saúde, Plano Odontológico, Wellhub (Gympass), Programa de Apoio ao Empregado, licença-maternidade e paternidade estendida, KIT parentalidade, auxílio-creche, Seguro de vida, Auxílio Funeral, Campanha vacinação, Empréstimo consignado, Programação anual, Parcerias SESC/SESI']</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Diagnóstico de problemas complexos', 'Análise de Vibração', 'Inspeção de rotinas diárias', 'Atualização de softwares'], 'tools_and_technologies': ['Softwares de equipamentos', 'Ferramentas de manutenção'], 'certifications': ['Formação Técnica'], 'soft_skills': ['Comprometimento', 'Responsabilidade', 'Trabalho em equipe', 'Segurança no trabalho'], 'inferred_skills': ['Capacidade de diagnóstico', 'Manutenção preventiva e corretiva'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub (Gympass)', 'Programa de Apoio ao Empregado', 'Licença-maternidade e paternidade estendida', 'KIT parentalidade', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/SESI']}</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>744000115712877</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Técnico HVAC I</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115712877</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>1 a 2 anos de experiência em instalação e manutenção de HVAC</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>['Hortolândia, Brasil']</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Curso Técnico - concluído</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>['Proficiência na instalação, manutenção e reparo de sistemas de HVAC', 'Capacidade de ler e interpretar projetos e esquemas', 'Fortes habilidades de diagnóstico e resolução de problemas', 'Conhecimento dos protocolos e regulamentos de segurança na indústria de HVAC', 'Familiaridade com várias ferramentas e equipamentos de HVAC', 'Conhecimentos básicos de informática', 'Carteira de motorista válida', 'Inglês intermediário', 'Excelentes habilidades de atendimento ao cliente e comunicação', 'Capacidade de trabalhar de forma independente e em equipe', 'Disponibilidade para trabalhar em horários administrativos e fins de semana']</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>744000115712877</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="b">
+        <v>1</v>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>['Descrição da empresa', 'Descrição do emprego', 'Qualificações', 'Informações Adicionais']</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Diagnóstico de problemas', 'Leitura de esquemas', 'Atendimento ao cliente'], 'tools_and_technologies': ['Ferramentas de instalação HVAC', 'Equipamentos de manutenção HVAC'], 'certifications': ['Certificação em HVAC'], 'soft_skills': ['Comunicação eficaz', 'Trabalho em equipe', 'Independência'], 'inferred_skills': ['Gestão de registros', 'Conformidade com regulamentos'], 'benefits': ['PLR', 'Plano de Saúde', 'Plano Odontológico', 'Wellhub (Gympass)', 'Assistência psicológica, social, jurídica e financeira', 'Licença-maternidade e paternidade estendida', 'KIT parentalidade', 'Auxílio-creche', 'Seguro de vida', 'Auxílio Funeral', 'Campanha vacinação', 'Empréstimo consignado', 'Calendário de feriados e dias pontes', 'Parcerias SESC/ SESI']}</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 250, 'total_tokens': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>744000115646818</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HVAC Prototype Fabricator</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115646818</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>3 years suggested minimum experience</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>['Unknown']</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2 year degree, HVAC training, or equivalent combination of education and experience</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>['reading wiring diagrams', 'modifying unit wiring and controls', 'sheet metal fabrication', 'brazing', 'welding', 'ability to lift equipment, compressors, units, motors, sheet metal parts']</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>744000115646818</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Competitive compensation package</t>
+        </is>
+      </c>
+      <c r="M251" t="b">
+        <v>1</v>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>['Company Description', 'Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': [], 'tools_and_technologies': ['wiring diagrams', 'sheet metal fabrication', 'brazing', 'welding'], 'certifications': ['HVAC training'], 'soft_skills': ['safety procedures', 'maintaining a clean work area'], 'inferred_skills': ['prototype testing', 'concept invention'], 'benefits': ['premium health coverage', '401(k) with matching', 'financial planning resources', 'paid time off', 'parental leave', 'life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 150, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>744000115541917</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Director, Source 1 Parts</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115541917</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>8+ years</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Business, Engineering, or Operations Management</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>['Aftermarket channel management', 'Marketing', 'Strategic sales programs', 'Channel conflict management', 'Cross-functional collaboration', 'Leadership']</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>On-site/Hybrid</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>744000115541917</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="b">
+        <v>1</v>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>['Job Responsibilities', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Advanced degree (MS or MBA)', 'Technical expertise in HVAC', 'Participation in industry associations (e.g., ASHRAE, HARDI)', 'Organizational transformation', 'Proficiency in Salesforce, SAP, Power BI', 'Cross-site and cross-business collaboration', 'Business acumen', 'Communication skills', 'Interpersonal skills', 'Six Sigma or lean methodologies'], 'tools_and_technologies': ['Salesforce', 'SAP', 'Power BI'], 'certifications': ['Six Sigma'], 'soft_skills': ['Leadership', 'Communication', 'Interpersonal skills', 'Influence', 'Collaboration'], 'inferred_skills': ['Strategic planning', 'Market analysis', 'Channel management', 'Operational efficiency'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>744000115480443</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Driver/Warehouse</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115480443</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2+ years of delivery driver experience of a commercial vehicle weighing 10k-26k pounds, 1+ years of experience working in a warehouse environment</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>['Delivery driving', 'Warehouse operations', 'Customer service', 'Inventory management', 'Safety compliance', 'Communication skills', 'Teamwork']</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>744000115480443</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="b">
+        <v>1</v>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Proficiency in Windows and Microsoft Office'], 'tools_and_technologies': ['Forklifts', 'Material handling equipment'], 'certifications': ['Valid licenses and certifications for vehicle operation'], 'soft_skills': ['Interpersonal skills', 'Decision-making', 'Organization', 'Professional communication'], 'inferred_skills': ['Safety management', 'Customer relationship management'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>744000115479968</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115479968</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2+ years of retail or customer service experience</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>['Jackson, TN']</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Point of Sale (POS) system operation', 'Product knowledge', 'Cash handling', 'Communication skills', 'Math skills', 'Teamwork', 'Problem-solving', 'Inventory management', 'Physical stamina']</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>744000115479968</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="b">
+        <v>1</v>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>['Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Forklift certification'], 'tools_and_technologies': ['Point of Sale (POS) systems'], 'certifications': ['Forklift certification (training provided)'], 'soft_skills': ['Customer engagement', 'Supportive attitude', 'Team collaboration', 'Problem-solving'], 'inferred_skills': ['Attention to detail', 'Multitasking', 'Physical endurance'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 150, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>744000115467118</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>COUNTER SALES ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115467118</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2+ years of retail or customer service experience</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>['Houston, TX']</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Point of Sale (POS) operation', 'Product knowledge', 'Cash handling', 'Communication skills', 'Math skills', 'Basic computer skills', 'Teamwork', 'Problem-solving', 'Inventory management']</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>744000115467118</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="b">
+        <v>1</v>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>['Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Forklift certification'], 'tools_and_technologies': ['Point of Sale (POS) systems'], 'certifications': ['Forklift certification (training provided)'], 'soft_skills': ['Customer engagement', 'Supportive attitude', 'Multitasking', 'Attention to detail', 'Collaboration', 'Problem-solving'], 'inferred_skills': [], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>744000115466246</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115466246</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2+ years of retail or customer service experience</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>['Spring, TX']</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Point of Sale (POS) operation', 'Product knowledge', 'Cash handling', 'Communication skills', 'Math skills', 'Teamwork', 'Problem-solving', 'Inventory management', 'Physical stamina']</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>744000115466246</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="b">
+        <v>1</v>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>['Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Forklift certification'], 'tools_and_technologies': ['Point of Sale (POS) systems'], 'certifications': ['Forklift certification (training provided)'], 'soft_skills': ['Customer engagement', 'Supportive attitude', 'Multitasking', 'Attention to detail', 'Collaboration'], 'inferred_skills': ['Problem-solving', 'Inventory management'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>744000115458082</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Quality Engineer (PPAP)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115458082</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Experience in manufacturing quality, process engineering, or related technical roles.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>['Germany']</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in engineering</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>['Knowledge of ISO 9001 Quality Management Systems', 'Proficiency in problem-solving tools (8D, 5 Why, Ishikawa, A3)', 'Ability to read and interpret technical drawings and specifications', 'Strong analytical, communication, and cross-functional collaboration skills']</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>744000115458082</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M257" t="b">
+        <v>1</v>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>['Job Description', 'Qualifications', 'Preferred Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Six Sigma', 'Experience in HVAC, automotive, or high-volume manufacturing environments', 'Knowledge of APQP, PPAP, PFMEA, Control Plans, MSA, and SPC', 'Experience with supplier defect notifications', 'Lean or Six Sigma certification (Green Belt preferred)'], 'tools_and_technologies': ['Metrology equipment (including CMM)', 'Measurement systems &amp; MSA tools', 'Problem-solving tools (8D, 5 Why, Ishikawa, A3)'], 'certifications': ['Lean or Six Sigma Green Belt'], 'soft_skills': ['Analytical skills', 'Communication skills', 'Cross-functional collaboration'], 'inferred_skills': ['Process documentation', 'Audit participation', 'Supplier quality management'], 'benefits': ['Premium health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 350, 'total_tokens': 600}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>744000115457447</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Quality Engineer – Distribution Center</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115457447</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Experience in manufacturing quality, process engineering, or related technical roles.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>['Distribution Center']</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in engineering</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>['Knowledge of ISO 9001 Quality Management Systems', 'Proficiency in problem-solving tools (8D, 5 Why, Ishikawa, A3)', 'Ability to read and interpret technical drawings and specifications', 'Strong analytical, communication, and cross-functional collaboration skills']</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>744000115457447</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="b">
+        <v>1</v>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>['Company Description', 'Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Experience in HVAC, automotive, or high-volume manufacturing environments', 'Knowledge of APQP, PPAP, PFMEA, Control Plans, MSA, and SPC', 'Experience with supplier defect notifications', 'Lean or Six Sigma certification (Green Belt preferred)'], 'tools_and_technologies': ['ISO 9001', '8D, 5 Why, Ishikawa, A3', 'Lean tools (5S, standardization, Poka-Yoke, Kaizen)'], 'certifications': ['Lean or Six Sigma Green Belt'], 'soft_skills': ['Analytical skills', 'Communication skills', 'Cross-functional collaboration'], 'inferred_skills': ['Problem-solving', 'Process improvement', 'Quality management'], 'benefits': ['Premium health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>744000115406318</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Aftersales Technical Tele-Support Engineer</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115406318</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>['Maidenhead, UK']</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>NVQ Level 2 - Refrigeration &amp; Air Conditioning, NVQ Level 3 - Refrigeration &amp; Air Conditioning, Safe Handling of Refrigerant, Proven HVAC experience, Full UK Driving Licence</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>['Strong technical knowledge', 'Problem-solving ability', 'Confident communication', 'Customer relationship building', 'Presentation and training delivery', 'Organizational skills', 'Detail-oriented']</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>On-site/Telephone support</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>744000115406318</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="b">
+        <v>1</v>
+      </c>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>['Job Description', 'Qualifications', 'Benefits']</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer communication', 'Technical support', 'Training delivery'], 'tools_and_technologies': ['Telephone', 'Email', 'On-site diagnostics'], 'certifications': ['NVQ Level 2 - Refrigeration &amp; Air Conditioning', 'NVQ Level 3 - Refrigeration &amp; Air Conditioning', 'Safe Handling of Refrigerant'], 'soft_skills': ['Customer relationship management', 'Communication skills', 'Organizational skills'], 'inferred_skills': ['Problem-solving', 'Technical troubleshooting', 'Training skills'], 'benefits': ['25 days annual leave plus bank holidays', 'Company Performance Bonus', 'Enhanced pension contributions', 'Cycle to work scheme', 'Family support policies', 'Access to Bosch training platform']}</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>744000115408458</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Specification Account Manager</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115408458</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Proven experience in HVAC specification sales, technical sales, or HVAC design engineering</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>['UK']</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Degree in Mechanical Engineering or related HVAC discipline, or equivalent technical experience</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>['HVAC system design principles', 'Industry standards (CIBSE, ASHRAE)', 'Interpreting HVAC drawings and schematics', 'Communication and presentation skills', 'Organizational skills', 'CRM proficiency', 'Technical support and proposal preparation']</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>On-site / Hybrid</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>744000115408458</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="b">
+        <v>1</v>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>['Benefits include 25 days annual leave, company bonus, pension, cycle scheme, family support, training platform']</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC specification sales', 'Technical sales', 'HVAC design engineering'], 'tools_and_technologies': ['CRM systems', 'Office software'], 'certifications': ['CIBSE', 'ASHRAE'], 'soft_skills': ['Communication', 'Presentation', 'Organizational skills', 'Influencing decision-makers'], 'inferred_skills': ['Project management', 'Market trend analysis', 'Regulatory compliance'], 'benefits': ['Annual leave', 'Performance bonus', 'Pension', 'Cycle to work', 'Family policy', 'Training programs']}</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>744000115404867</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Indirect Account Manager</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115404867</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Proven technical experience with HVAC, managing indirect channels or distribution networks, strong CRM and forecasting proficiency</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>['UK']</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Proven technical experience in HVAC, knowledge of Hitachi HVAC or competitors</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>['Channel Sales Leadership', 'Distributor Relationship Management', 'Channel Strategy &amp; Enablement', 'Sales Planning &amp; Reporting', 'CRM Discipline &amp; Administration', 'Forecasting &amp; Supply Coordination', 'Training &amp; Development', 'Market Engagement']</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>On-site / Hybrid</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>744000115404867</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M261" t="b">
+        <v>1</v>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>['Benefits include 25 days annual leave, company bonus, pension, cycle scheme, family support, training platform']</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC knowledge', 'Channel management', 'Sales strategy', 'Customer training'], 'tools_and_technologies': ['CRM software', 'PowerPoint'], 'certifications': ['HVAC technical certification'], 'soft_skills': ['Leadership', 'Communication', 'Strategic thinking', 'Customer relationship management'], 'inferred_skills': ['Market analysis', 'Supply chain coordination'], 'benefits': ['Annual leave', 'Performance bonus', 'Pension', 'Cycle to work scheme', 'Family support policies', 'Training programs']}</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>744000115065685</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HVAC Account Manager</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115065685</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>5+ years of commercial HVAC technical knowledge, 5+ years of customer service experience</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>High School Diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>['Commercial HVAC technical knowledge', 'Customer service', 'Supporting sales team', 'Proficiency in Windows and Microsoft Office', 'Interpersonal skills', 'Customer relationship management', 'Decision-making skills', 'Communication skills', 'Organizational skills', 'Analytical skills']</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>744000115065685</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="b">
+        <v>1</v>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>['Job Responsibilities', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Proficiency in Windows and Microsoft Office', 'Strong interpersonal skills', 'Customer relationship skills', 'Decision-making skills', 'Effective communication', 'Organizational skills', 'Analytical skills'], 'tools_and_technologies': ['Microsoft Office'], 'certifications': [], 'soft_skills': ['Interpersonal skills', 'Customer relationship management', 'Decision-making', 'Communication', 'Organization', 'Analytical thinking'], 'inferred_skills': ['Sales support', 'Technical support', 'Product knowledge', 'Customer training'], 'benefits': ['Leadership coaching', 'Career development', 'Inclusive culture']}</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 250, 'output_tokens': 300, 'total_tokens': 550}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>744000115010460</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Counter Sales Associate</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000115010460</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2+ years of retail or customer service experience</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>High School diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>['Interpersonal skills', 'Customer relationship management', 'Decision-making skills', 'Effective communication', 'Organization skills', 'Teamwork', 'Analytical skills', 'Proficiency in Windows and Microsoft Office', 'HVAC industry experience (preferred)', 'Warehouse and forklift operations (preferred)']</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>744000115010460</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="b">
+        <v>1</v>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service', 'Team collaboration', 'Problem resolution'], 'tools_and_technologies': ['Microsoft Office', 'Windows'], 'certifications': [], 'soft_skills': ['Communication', 'Organization', 'Decision-making', 'Teamwork'], 'inferred_skills': ['Customer relationship management', 'Order processing', 'Problem solving'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>744000114735903</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Tool Crib Supervisor</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114735903</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>3+ years</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>['Wichita, Kansas']</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>['inventory management', 'supervisory experience', 'safety protocols', 'team leadership', 'data analysis', 'computer proficiency', 'organizational skills', 'communication skills', 'problem-solving']</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>744000114735903</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="b">
+        <v>1</v>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>['Preferred Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['ERP software', 'bill of goods validation', 'Lean manufacturing', 'certification in forklift or material handling', 'quality control', 'manufacturing experience'], 'tools_and_technologies': ['inventory management systems', 'computer software'], 'certifications': ['Forklift certification', 'Material handling certification'], 'soft_skills': ['team motivation', 'training', 'communication', 'organization', 'problem-solving'], 'inferred_skills': ['process improvement', 'data analysis', 'compliance management'], 'benefits': ['health coverage', '401(k) with matching', 'paid time off', 'parental leave', 'life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>744000114697808</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Warranty specialist 1</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114697808</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>['Monterrey, Mexico']</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent; Associate's degree in Business Administration or related field preferred</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Warranty processing', 'Verbal and written communication in English and Spanish', 'Proficiency in Microsoft Office Suite', 'Problem-solving', 'Analytical skills', 'Attention to detail', 'Time management', 'Knowledge of warranty policies and procedures', 'Understanding of automotive or consumer electronics industries']</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>744000114697808</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="b">
+        <v>1</v>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service', 'Warranty processing', 'Communication in English and Spanish', 'Problem-solving', 'Analytical skills'], 'tools_and_technologies': ['Microsoft Office Suite', 'Warranty management systems'], 'certifications': [], 'soft_skills': ['Attention to detail', 'Time management', 'Customer-focused mindset', 'Teamwork'], 'inferred_skills': [], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 150, 'total_tokens': 300}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>744000114693121</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Director Norman Modification Center</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114693121</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>15+ years in related fields, 2+ years leading teams</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>['Norman, OK']</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in engineering</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>['System design', 'Application', 'Product management', 'Field sales', 'Leadership', 'Business management', 'Technical knowledge of HVAC equipment']</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>744000114693121</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="b">
+        <v>1</v>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['Responsibilities', 'Qualifications']</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['MBA', 'Financial Statements', 'Team management', 'Cross-functional influence'], 'tools_and_technologies': ['Market data analysis', 'Product performance tools'], 'certifications': [], 'soft_skills': ['Communication', 'Decision making', 'Leadership', 'Adaptability'], 'inferred_skills': ['Strategic planning', 'Customer relationship management', 'Competitive intelligence'], 'benefits': ['Growth opportunities', 'Innovative culture', 'Career development']}</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>744000114664411</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Sales Executive HVAC SPAIN</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114664411</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Minimum of 5 years</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>['Cataluña, Spain']</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>['Technical and commercial sales experience in HVAC', 'Advanced technical knowledge of HVAC products', 'Knowledge of equipment selection software', 'Experience using Salesforce CRM', 'Good level of English and Spanish', 'Organized with excellent communication skills', 'Proactive attitude', 'Results-oriented']</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>744000114664411</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="b">
+        <v>1</v>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>['Develop, manage, and expand client portfolio', 'Conduct technical analyses and oversee implementation', 'Prepare cost proposals and budgets', 'Organize training sessions, technical visits, and meetings', 'Manage project tracking from inception to sale', 'Conduct market analysis']</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Client relationship management', 'Project management'], 'tools_and_technologies': ['Salesforce CRM', 'Equipment selection software'], 'certifications': [], 'soft_skills': ['Communication skills', 'Proactivity', 'Teamwork', 'Independence'], 'inferred_skills': ['Market analysis', 'Strategic planning'], 'benefits': []}</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>744000114449446</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Production Manager (2nd shift - 3:30PM - 2:00AM)</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114449446</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Minimum of eight (8) years of experience as a Production Manager/Production Supervisor in a manufacturing/production environment</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or equivalent combination of education and experience</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>['Proficiency using MS Office Suite', 'Experience and certification in Lean Manufacturing and Continuous Improvement (preferred)']</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>744000114449446</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="b">
+        <v>1</v>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>['Company Description', 'Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Lean Manufacturing', 'Continuous Improvement'], 'tools_and_technologies': ['MS Office Suite'], 'certifications': ['Lean Manufacturing Certification'], 'soft_skills': ['Leadership', 'Teamwork', 'Inclusion', 'Problem Solving'], 'inferred_skills': ['Safety Management', 'Quality Control', 'Operational Planning'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 150, 'output_tokens': 250, 'total_tokens': 400}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>744000114429028</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Production Manager (1st Shift - 5:00AM - 3:30PM)</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114429028</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>10+ years in manufacturing environments, 3+ years of production supervision, 5+ years of factory experience in Manufacturing, Quality, Engineering, or Production Planning</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>['Norman, Oklahoma']</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Associate's degree or Bachelor's Degree in Engineering, Business Administration, or related field</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>['Production planning', 'Scheduling', 'Quality control management', 'Lean manufacturing principles', 'ERP systems (SAP, Oracle)', 'Microsoft Office Suite', 'Analytical and problem-solving skills', 'Supply chain management', 'Manufacturing processes and technologies', 'Regulations and safety standards', 'Communication and interpersonal skills', 'Decisive decision-making', 'Process improvements', 'Organizational skills']</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>744000114429028</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Competitive salary with benefits</t>
+        </is>
+      </c>
+      <c r="M269" t="b">
+        <v>1</v>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>['Company Description', 'Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Six Sigma certification', 'Safety management', 'OSHA compliance', 'Budget management', 'Cost control', 'Experience with coil manufacturing', 'Robotic paint application'], 'tools_and_technologies': ['ERP systems (SAP, Oracle)', 'Microsoft Office Suite'], 'certifications': ['Six Sigma'], 'soft_skills': ['Communication', 'Interpersonal skills', 'Decisiveness', 'Organizational skills', 'Team leadership'], 'inferred_skills': ['Operational excellence', 'Continuous improvement', 'Resource optimization', 'Safety compliance'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 350, 'output_tokens': 250, 'total_tokens': 600}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>744000114113651</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Machine Operator III, Weekend 2nd Shift</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114113651</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>['Norman, United States']</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>['Operating complex machinery', 'Interpreting technical manuals and blueprints', 'Routine maintenance and troubleshooting', 'Data entry and report generation', 'Quality control standards', 'Preventive maintenance procedures', 'Safety protocols']</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>744000114113651</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="b">
+        <v>1</v>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>['Schedule: Friday - Sunday 5pm - 5am plus overtime', 'Physical ability to stand and lift up to 50 pounds', 'Willingness to commute to Norman, US for weekends']</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Technical certifications related to machine operation'], 'tools_and_technologies': ['Manufacturing equipment', 'Computer systems for data entry and reporting'], 'certifications': [], 'soft_skills': ['Attention to detail', 'Time management', 'Organizational skills', 'Teamwork', 'Independence'], 'inferred_skills': ['Problem-solving', 'Safety awareness', 'Quality assurance'], 'benefits': ['Equal Opportunity Employer', 'Work-life balance initiatives', 'Continuous improvement participation']}</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>744000114105327</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Counter sales associate</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114105327</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>['Portland, United States']</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent; Associate's degree preferred</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>['Customer service', 'Verbal and written communication', 'Active listening', 'Problem-solving', 'Computer proficiency (CRM software, Microsoft Office)', 'Multi-tasking', 'Patience and empathy', 'Teamwork']</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>744000114105327</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="b">
+        <v>1</v>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>['Job Description', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['Customer service', 'Communication', 'Problem-solving', 'Teamwork'], 'tools_and_technologies': ['CRM software', 'Microsoft Office'], 'certifications': [], 'soft_skills': ['Empathy', 'Patience', 'Professionalism'], 'inferred_skills': ['Order processing', 'Inventory management', 'Safety procedures'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>744000114075483</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>National HVAC Store Readiness Training Manager</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Bosch-HomeComfort</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Bosch-HomeComfort/744000114075483</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>5+ years in HVAC distribution environment</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>['North America']</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>['HVAC distribution knowledge', 'Operational expertise', 'Training facilitation', 'Inventory management', 'Customer service', 'Team management', 'Distribution processes', 'Technical HVAC product knowledge']</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>On-site with extensive travel</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>744000114075483</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Competitive, not specified</t>
+        </is>
+      </c>
+      <c r="M272" t="b">
+        <v>1</v>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>['Store Launch Training Delivery', 'Functional Training Programs', 'HVAC Distribution Operational Support', 'Training Evaluation &amp; Continuous Improvement', 'Cross-Functional Collaboration', 'Qualifications', 'Additional Information']</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>{'preferred_skills': ['HVAC distribution', 'Training delivery', 'Operational knowledge', 'Technical HVAC skills', 'Travel flexibility'], 'tools_and_technologies': ['Warehouse management systems', 'Store merchandising tools', 'Operational workflows'], 'certifications': [], 'soft_skills': ['Interpersonal skills', 'Relationship building', 'Adaptability', 'Feedback reception', 'Collaboration'], 'inferred_skills': ['Leadership', 'Performance assessment', 'Strategic planning'], 'benefits': ['Health coverage', '401(k) with matching', 'Paid time off', 'Parental leave', 'Life and disability protection']}</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>{'input_tokens': 0, 'output_tokens': 0, 'total_tokens': 0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
